--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -13552,7 +13552,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>Havenas haaks op de kust (azimut 102 gr), kustpunt A1 E 296.650,0 / N 7.648.300,0; tussen kustbebouwing (zuid, N ca. 7.646.300) en zichtbaar grondwerk (noord, N ca. 7.650.000); rivier en wetland in het zuidwesten vermeden.</t>
+          <t>Locatie vastgesteld: Porto Central, Presidente Kennedy - Espírito Santo (29350-000). Havenas haaks op de kust (azimut 110 gr) door het bouwterrein fase 1; kustpunt A1 E 297.135,0 / N 7.650.000,0; bekkens landinwaarts op het Porto Central-terrein.</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B01; vervolg: Eigendom/bestemming en relatie met het werkelijke Porto Central-terrein bij de begeleider navragen.</t>
+          <t>Besluitenlijst B01; vervolg: Ligging van de havenas op het terrein afstemmen met het bouwterrein fase 1 / masterplan.</t>
         </is>
       </c>
       <c r="F22" s="1" t="n"/>
@@ -15604,16 +15604,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>296650</v>
+        <v>297135</v>
       </c>
       <c r="D39" t="n">
-        <v>7648300</v>
+        <v>7650000</v>
       </c>
       <c r="E39" t="n">
-        <v>-21.2556262</v>
+        <v>-21.2403293</v>
       </c>
       <c r="F39" t="n">
-        <v>-40.9597006</v>
+        <v>-40.9548262</v>
       </c>
     </row>
     <row r="40">
@@ -15628,16 +15628,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>297090.17</v>
+        <v>297557.86</v>
       </c>
       <c r="D40" t="n">
-        <v>7648206.44</v>
+        <v>7649846.09</v>
       </c>
       <c r="E40" t="n">
-        <v>-21.2565204</v>
+        <v>-21.2417663</v>
       </c>
       <c r="F40" t="n">
-        <v>-40.9554718</v>
+        <v>-40.9507715</v>
       </c>
     </row>
     <row r="41">
@@ -15652,16 +15652,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>298753.02</v>
+        <v>299155.34</v>
       </c>
       <c r="D41" t="n">
-        <v>7647852.99</v>
+        <v>7649264.66</v>
       </c>
       <c r="E41" t="n">
-        <v>-21.2598972</v>
+        <v>-21.2471941</v>
       </c>
       <c r="F41" t="n">
-        <v>-40.9394954</v>
+        <v>-40.9354532</v>
       </c>
     </row>
     <row r="42">
@@ -15676,16 +15676,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>300220.24</v>
+        <v>300564.88</v>
       </c>
       <c r="D42" t="n">
-        <v>7647541.12</v>
+        <v>7648751.63</v>
       </c>
       <c r="E42" t="n">
-        <v>-21.2628755</v>
+        <v>-21.2519822</v>
       </c>
       <c r="F42" t="n">
-        <v>-40.9253979</v>
+        <v>-40.921936</v>
       </c>
     </row>
     <row r="43">
@@ -15700,16 +15700,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>308534.49</v>
+        <v>308552.27</v>
       </c>
       <c r="D43" t="n">
-        <v>7645773.87</v>
+        <v>7645844.46</v>
       </c>
       <c r="E43" t="n">
-        <v>-21.2797312</v>
+        <v>-21.2790957</v>
       </c>
       <c r="F43" t="n">
-        <v>-40.8454996</v>
+        <v>-40.8453204</v>
       </c>
     </row>
     <row r="44">
@@ -15724,16 +15724,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>296871.99</v>
+        <v>297540.35</v>
       </c>
       <c r="D44" t="n">
-        <v>7649632.97</v>
+        <v>7651289.11</v>
       </c>
       <c r="E44" t="n">
-        <v>-21.2436142</v>
+        <v>-21.2287338</v>
       </c>
       <c r="F44" t="n">
-        <v>-40.9574032</v>
+        <v>-40.9507688</v>
       </c>
     </row>
     <row r="45">
@@ -15748,16 +15748,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>296248.26</v>
+        <v>296514.29</v>
       </c>
       <c r="D45" t="n">
-        <v>7646698.53</v>
+        <v>7648470.03</v>
       </c>
       <c r="E45" t="n">
-        <v>-21.2700425</v>
+        <v>-21.2540757</v>
       </c>
       <c r="F45" t="n">
-        <v>-40.9637624</v>
+        <v>-40.9609876</v>
       </c>
     </row>
     <row r="46">
@@ -15772,16 +15772,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>296158.8</v>
+        <v>296695.12</v>
       </c>
       <c r="D46" t="n">
-        <v>7648634.43</v>
+        <v>7650399.54</v>
       </c>
       <c r="E46" t="n">
-        <v>-21.2525512</v>
+        <v>-21.2366723</v>
       </c>
       <c r="F46" t="n">
-        <v>-40.9643922</v>
+        <v>-40.9590153</v>
       </c>
     </row>
     <row r="47">
@@ -15796,16 +15796,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>294593.76</v>
+        <v>295191.62</v>
       </c>
       <c r="D47" t="n">
-        <v>7648967.09</v>
+        <v>7650946.77</v>
       </c>
       <c r="E47" t="n">
-        <v>-21.2493709</v>
+        <v>-21.2315619</v>
       </c>
       <c r="F47" t="n">
-        <v>-40.9794274</v>
+        <v>-40.9734306</v>
       </c>
     </row>
     <row r="48">
@@ -15820,16 +15820,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>297253.57</v>
+        <v>297545.53</v>
       </c>
       <c r="D48" t="n">
-        <v>7646955.12</v>
+        <v>7648584.21</v>
       </c>
       <c r="E48" t="n">
-        <v>-21.2678381</v>
+        <v>-21.2531599</v>
       </c>
       <c r="F48" t="n">
-        <v>-40.9540468</v>
+        <v>-40.9510404</v>
       </c>
     </row>
     <row r="49">
@@ -15844,16 +15844,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>294351.35</v>
+        <v>294926.72</v>
       </c>
       <c r="D49" t="n">
-        <v>7648788.59</v>
+        <v>7650803.75</v>
       </c>
       <c r="E49" t="n">
-        <v>-21.2509553</v>
+        <v>-21.2328236</v>
       </c>
       <c r="F49" t="n">
-        <v>-40.9817839</v>
+        <v>-40.9759991</v>
       </c>
     </row>
   </sheetData>

--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="C6" s="43" t="n">
-        <v>2192085</v>
+        <v>3122965</v>
       </c>
       <c r="D6" s="35" t="n"/>
       <c r="E6" s="32">
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>3079000</v>
+        <v>3019000</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
@@ -13577,22 +13577,22 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Havenmond</t>
+          <t>Havenvorm</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>DO: dammen verlegd, 350 m vrij tussen de golfbrekerfootprints (90 m breed).</t>
+          <t>DO: vorm van het masterplan aangehouden: twee gebogen dammen met ingang naar het OZO (11/14), hoofdbekken langs de noordzijde met graan aan de noordkade (10), containervinger met kade aan de voorhaven (6), insteekbekken en tweede vinger (7/8), tank- en energiezone langs de zuidrand (9) en LNG-steiger bij de zuidelijke dam (18). Maten volgen het rekenboek, niet het masterplan.</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Verwerkt</t>
+          <t>Vastgelegd</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B02; vervolg: Na golfbrekerontwerp (kruin, taluds) footprint en vrije breedte opnieuw meten.</t>
+          <t>Besluitenlijst B02; vervolg: Masterplan-functies buiten het groepsprogramma (erts, olie, werf) als reserve aangeduid.</t>
         </is>
       </c>
       <c r="F23" s="1" t="n"/>
@@ -13607,12 +13607,12 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Draaikom en stopweg</t>
+          <t>Havenmond</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>DO: middelpunt 450 m uit de kust, mond op 2.150 m: stopweg 1.700 m = 5,1 LOA; draaikom 687 m vrij van afgemeerde schepen en 281 m van kades/dammen.</t>
+          <t>DO: dammen verlegd, 350 m vrij tussen de golfbrekerfootprints (90 m breed).</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -13622,7 +13622,7 @@
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B03; vervolg: Nautische (simulator)toets met sleepboten.</t>
+          <t>Besluitenlijst B03; vervolg: Na golfbrekerontwerp (kruin, taluds) footprint en vrije breedte opnieuw meten.</t>
         </is>
       </c>
       <c r="F24" s="1" t="n"/>
@@ -13637,22 +13637,22 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Toegangsgeul</t>
+          <t>Draaikom en stopweg</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>DO: rechte geul, 220 m bodembreedte, -18,20 m MLWS, as in het verlengde van de havenas. Lengte buiten de mond voorlopig 10.000 m.</t>
+          <t>DO: draaikom 200 m zeewaarts verschoven, mond verder uit de kust: stopweg 1.700 m = 5,1 LOA; draaikom 87 m vrij van afgemeerde schepen en 140 m van kades/dammen.</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Deels open</t>
+          <t>Verwerkt</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B04; vervolg: Eindpunt op de -18,2 m MLWS-dieptelijn van de bathymetrische kaart leggen; MLWS-DHN koppelen; geullengte terugzetten in Nautiek D31.</t>
+          <t>Besluitenlijst B04; vervolg: Nautische (simulator)toets met sleepboten; containerschepen varen na het draaien achteruit of met sleepboten naar C2-C4.</t>
         </is>
       </c>
       <c r="F25" s="1" t="n"/>
@@ -13667,22 +13667,22 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Sleepbootkoppelpunt</t>
+          <t>Toegangsgeul en sleepboten</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>DO: koppelpunt op de geulas, 1.500 m buiten de mond (A4).</t>
+          <t>DO: rechte geul 220 m, -18,20 m MLWS, in het verlengde van de havenmond; koppelpunt 1.500 m buiten de mond (A4). Lengte buiten de mond voorlopig 10.000 m.</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Verwerkt</t>
+          <t>Deels open</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B05; vervolg: Bevestigen met loods/sleepdienst en golfklimaat (werkbaarheid).</t>
+          <t>Besluitenlijst B05; vervolg: Eindpunt op de -18,2 m MLWS-dieptelijn van de bathymetrie leggen; MLWS-DHN koppelen; geullengte terugzetten in Nautiek D31.</t>
         </is>
       </c>
       <c r="F26" s="1" t="n"/>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>DO: LNG-steiger aan de lijzijde van de zuidelijke dam in eigen insteek, 762 m vrij van de draaikom; tankzone 25 ha met 3 x 180.000 m3 en ruimte voor een 4e tank; 291 m tot RoRo-terrein.</t>
+          <t>DO: tank- en energiezone verschoven naar de zuidrand (masterplan 9); tanks op 465 m van het containerterrein, weg-/spoorcorridor ertussen; LNG-ligplaats 939 m vrij van de draaikom; ruimte voor een 4e tank.</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>DO: ieder 30 ha (500 x 600 m) met eigen kade van 300 m, eigen inrit; weg en spoor achter de percelen.</t>
+          <t>DO: graan 30 ha aan de noordkade (masterplan 10) met silo en transportband; RoRo 30 ha op de tweede vinger aan het insteekbekken (masterplan 7/8), ieder een eigen kade van 300 m en eigen inrit.</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>DO: fase 1 bij de ingang; binnenbekken in drie stappen (72,0 / 81,0 / 105,8 ha); uitbreiding aan het doodlopende eind, geen vaarwegblokkade.</t>
+          <t>DO: fase 1 bij de ingang (C1-C2), kade groeit zuidwaarts; bekkens gebaggerd 184,2 / 210,2 / 236,2 ha; reserve-insteek en hoofdbekken-west (96,8 ha) pas in fase 4.</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>DO: reservering 49,5 ha naast de LNG-zone; koelwaterinlaat in de voorhaven en uitlaat buiten de zuidelijke dam (indicatief).</t>
+          <t>DO: reservering 52,5 ha in de zuidelijke energiezone; gasleiding naar het regionale net; koelwaterinlaat in de voorhaven, uitlaat buiten de zuidelijke dam (indicatief).</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>DO: hoofdweg + spoor in corridor aan de westzijde, takken achter de terminalpercelen met aparte poorten.</t>
+          <t>DO: hoofdweg + spoor aan de westzijde (zoals de ringweg in het masterplan), takken achter de percelen: noord (graan), midden (RoRo), zuid (containers, LNG, centrale); aparte poorten.</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Havenbekken 2.192.085 m2, geul buiten de mond 2.200.000 m2, terreinophoging 3.079.000 m2 ingevuld.</t>
+          <t>Havenbekken 3.122.965 m2, geul buiten de mond 2.200.000 m2, terreinophoging 3.019.000 m2 ingevuld; ontwerpbodem als LandXML-oppervlak voor Civil 3D.</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B12; vervolg: Bestaande diepten/hoogten uit bathymetrie en hoogtemodel invoeren; geul splitsen op DHN -15 m.</t>
+          <t>Besluitenlijst B12; vervolg: Bathymetrie als Civil 3D-oppervlak inlezen en volume tegen Ontwerpbodem_DO berekenen; geul splitsen op DHN -15 m.</t>
         </is>
       </c>
       <c r="F33" s="1" t="n"/>
@@ -14650,7 +14650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>687</v>
+        <v>87</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>762</v>
+        <v>939</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -15304,32 +15304,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LNG-zone (tanks + hervergassing)</t>
+          <t>LNG-tanks tot containerterrein</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Invoer D51-D52</t>
-        </is>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3 tanks + optie 4e</t>
+          <t>QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Centrale + utilities (reservering)</t>
+          <t>LNG-zone (tanks + hervergassing)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -15338,23 +15334,23 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>49.5</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>geen vast oppervlak</t>
+          <t>Invoer D51-D52</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>3 tanks + optie 4e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Havendiensten / sleepboten</t>
+          <t>Centrale + utilities (reservering)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -15363,9 +15359,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+        <v>52.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>geen vast oppervlak</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>reservering</t>
@@ -15375,7 +15375,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Reserveterreinen</t>
+          <t>Havendiensten / sleepboten</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -15384,7 +15384,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>161.1</v>
+        <v>15.4</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
@@ -15396,48 +15396,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vrije breedte binnenbekken (schepen aan beide zijden)</t>
+          <t>Reserveterreinen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>354</v>
-      </c>
-      <c r="D29" t="n">
-        <v>220</v>
+        <v>237.8</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>reservering</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 1</t>
+          <t>Vrije breedte insteekbekken met RoRo-schip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>720000</v>
+        <v>407</v>
+      </c>
+      <c r="D30" t="n">
+        <v>220</v>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>voldoet</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
+          <t>Binnenbekken gebaggerd fase 1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -15446,7 +15450,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>810000</v>
+        <v>1842500</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -15454,7 +15458,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
+          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -15463,7 +15467,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1057500</v>
+        <v>2102500</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -15471,7 +15475,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Voorhaven + LNG-insteek gebaggerd</t>
+          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -15480,7 +15484,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1134585</v>
+        <v>2362500</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -15488,7 +15492,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Havenbekken totaal (zone 1)</t>
+          <t>Voorhaven + LNG-insteek gebaggerd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15497,23 +15501,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2192085</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Grondwerk C6</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ingevuld</t>
-        </is>
-      </c>
+        <v>760465</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Geul buiten de mond (zone 2 + 3)</t>
+          <t>Havenbekken totaal (zone 1)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15522,338 +15518,387 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2200000</v>
+        <v>3122965</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grondwerk C7 + C8</t>
+          <t>Grondwerk C6</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>splitsing open</t>
+          <t>ingevuld</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Geul buiten de mond (zone 2 + 3)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Grondwerk C7 + C8</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>splitsing open</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>3079000</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="C37" t="n">
+        <v>3019000</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>Grondwerk D21</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>ingevuld</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Punt</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Omschrijving</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>E (m)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>N (m)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Lon</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Punt</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kustpunt havenas (waterlijn)</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>297135</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7650000</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-21.2403293</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-40.9548262</v>
+          <t>Omschrijving</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>E (m)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>N (m)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Lat</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lon</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Middelpunt vrije draaikom</t>
+          <t>Kustpunt havenas (waterlijn)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>297557.86</v>
+        <v>297135</v>
       </c>
       <c r="D40" t="n">
-        <v>7649846.09</v>
+        <v>7650000</v>
       </c>
       <c r="E40" t="n">
-        <v>-21.2417663</v>
+        <v>-21.2403293</v>
       </c>
       <c r="F40" t="n">
-        <v>-40.9507715</v>
+        <v>-40.9548262</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Midden havenmond</t>
+          <t>Middelpunt vrije draaikom</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>299155.34</v>
+        <v>297451.11</v>
       </c>
       <c r="D41" t="n">
-        <v>7649264.66</v>
+        <v>7649991.36</v>
       </c>
       <c r="E41" t="n">
-        <v>-21.2471941</v>
+        <v>-21.2404426</v>
       </c>
       <c r="F41" t="n">
-        <v>-40.9354532</v>
+        <v>-40.9517825</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sleepbootkoppelpunt</t>
+          <t>Midden havenmond</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>300564.88</v>
+        <v>298876.85</v>
       </c>
       <c r="D42" t="n">
-        <v>7648751.63</v>
+        <v>7649065.48</v>
       </c>
       <c r="E42" t="n">
-        <v>-21.2519822</v>
+        <v>-21.2489619</v>
       </c>
       <c r="F42" t="n">
-        <v>-40.921936</v>
+        <v>-40.9381592</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eindpunt geul (voorlopig)</t>
+          <t>Sleepbootkoppelpunt</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>308552.27</v>
+        <v>300134.86</v>
       </c>
       <c r="D43" t="n">
-        <v>7645844.46</v>
+        <v>7648248.52</v>
       </c>
       <c r="E43" t="n">
-        <v>-21.2790957</v>
+        <v>-21.2564782</v>
       </c>
       <c r="F43" t="n">
-        <v>-40.8453204</v>
+        <v>-40.9261374</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wortel noordelijke golfbreker</t>
+          <t>Eindpunt geul (voorlopig)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>297540.35</v>
+        <v>307263.56</v>
       </c>
       <c r="D44" t="n">
-        <v>7651289.11</v>
+        <v>7643619.09</v>
       </c>
       <c r="E44" t="n">
-        <v>-21.2287338</v>
+        <v>-21.2990555</v>
       </c>
       <c r="F44" t="n">
-        <v>-40.9507688</v>
+        <v>-40.8579896</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wortel zuidelijke golfbreker</t>
+          <t>Wortel noordelijke golfbreker</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>296514.29</v>
+        <v>297737.85</v>
       </c>
       <c r="D45" t="n">
-        <v>7648470.03</v>
+        <v>7651802.52</v>
       </c>
       <c r="E45" t="n">
-        <v>-21.2540757</v>
+        <v>-21.2241196</v>
       </c>
       <c r="F45" t="n">
-        <v>-40.9609876</v>
+        <v>-40.9488056</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Containerkade begin (F1)</t>
+          <t>Wortel zuidelijke golfbreker</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>296695.12</v>
+        <v>296314.32</v>
       </c>
       <c r="D46" t="n">
-        <v>7650399.54</v>
+        <v>7648329.97</v>
       </c>
       <c r="E46" t="n">
-        <v>-21.2366723</v>
+        <v>-21.255318</v>
       </c>
       <c r="F46" t="n">
-        <v>-40.9590153</v>
+        <v>-40.9629306</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Containerkade eind (F3)</t>
+          <t>Containerkade noordeinde (F1)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>295191.62</v>
+        <v>297135.17</v>
       </c>
       <c r="D47" t="n">
-        <v>7650946.77</v>
+        <v>7650585.23</v>
       </c>
       <c r="E47" t="n">
-        <v>-21.2315619</v>
+        <v>-21.2350446</v>
       </c>
       <c r="F47" t="n">
-        <v>-40.9734306</v>
+        <v>-40.9547548</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Midden LNG-ligplaats</t>
+          <t>Containerkade zuideinde (F3)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>297545.53</v>
+        <v>296587.94</v>
       </c>
       <c r="D48" t="n">
-        <v>7648584.21</v>
+        <v>7649081.73</v>
       </c>
       <c r="E48" t="n">
-        <v>-21.2531599</v>
+        <v>-21.2485603</v>
       </c>
       <c r="F48" t="n">
-        <v>-40.9510404</v>
+        <v>-40.960205</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Midden LNG-ligplaats</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>297377.21</v>
+      </c>
+      <c r="D49" t="n">
+        <v>7648560.34</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-21.2533567</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-40.9526645</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>A11</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Eind binnenbekken</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>294926.72</v>
-      </c>
-      <c r="D49" t="n">
-        <v>7650803.75</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-21.2328236</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-40.9759991</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Graankade midden</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>296729.58</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7651371.36</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-21.2279005</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-40.9585675</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RoRo-kade midden</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>295815.28</v>
+      </c>
+      <c r="D51" t="n">
+        <v>7650906.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-21.2320002</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-40.9674288</v>
       </c>
     </row>
   </sheetData>

--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>11700</v>
+        <v>11727</v>
       </c>
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>DO-tekening: 10.000 m buiten de mond (eindpunt A5 nog op -18,2 m MLWS-lijn leggen) + 1.700 m mond-draaikom</t>
+          <t>DO-tekening: 10.000 m buiten de mond (eindpunt A5 nog op -18,2 m MLWS-lijn leggen) + 1.727 m mond-draaikom</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="C6" s="43" t="n">
-        <v>3122965</v>
+        <v>2649198</v>
       </c>
       <c r="D6" s="35" t="n"/>
       <c r="E6" s="32">
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>3019000</v>
+        <v>3266194</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>DO: vorm van het masterplan aangehouden: twee gebogen dammen met ingang naar het OZO (11/14), hoofdbekken langs de noordzijde met graan aan de noordkade (10), containervinger met kade aan de voorhaven (6), insteekbekken en tweede vinger (7/8), tank- en energiezone langs de zuidrand (9) en LNG-steiger bij de zuidelijke dam (18). Maten volgen het rekenboek, niet het masterplan.</t>
+          <t>DO: de Porto Central-render is op schaal overgetrokken (10,035 m per pixel, op de kust gedraaid): gebogen dammen met ingang naar het OZO, hoofdbekken oost-west langs de noordkade, schuine vingers en insteekbekkens evenwijdig aan de kust, containervinger (6) met de kraankade aan de insteekzijde, tankpark langs de zuidrand (9) en LNG-steiger bij de zuidelijke dam (18). Zie blad DO-05.</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B02; vervolg: Masterplan-functies buiten het groepsprogramma (erts, olie, werf) als reserve aangeduid.</t>
+          <t>Besluitenlijst B02; vervolg: Olie- en droge-bulksteigers (4, 5), werf (3) en erts (2) vallen buiten het programma: weggelaten of reserve.</t>
         </is>
       </c>
       <c r="F23" s="1" t="n"/>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>DO: draaikom 200 m zeewaarts verschoven, mond verder uit de kust: stopweg 1.700 m = 5,1 LOA; draaikom 87 m vrij van afgemeerde schepen en 140 m van kades/dammen.</t>
+          <t>DO: draaikom in de voorhaven op de plaats van de -20 m-cirkel in de render; stopweg 1.727 m = 5,2 LOA; 646 m vrij van afgemeerde schepen en 230 m van kades/dammen.</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B04; vervolg: Nautische (simulator)toets met sleepboten; containerschepen varen na het draaien achteruit of met sleepboten naar C2-C4.</t>
+          <t>Besluitenlijst B04; vervolg: Nautische (simulator)toets: bocht van de toegang naar het insteekbekken (ca. 115 gr) met sleepboten.</t>
         </is>
       </c>
       <c r="F25" s="1" t="n"/>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>DO: tank- en energiezone verschoven naar de zuidrand (masterplan 9); tanks op 465 m van het containerterrein, weg-/spoorcorridor ertussen; LNG-ligplaats 939 m vrij van de draaikom; ruimte voor een 4e tank.</t>
+          <t>DO: LNG-tanks in het oostelijke deel van het tankpark (masterplan 9), 296 m van het containerterrein met de ringweg ertussen; LNG-steiger (18) 729 m vrij van de draaikom; ruimte voor een 4e tank.</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B06; vervolg: QRA en veiligheidsafstanden; N-1-voorraadbeleid kiezen (4e tank of kleiner buffer).</t>
+          <t>Besluitenlijst B06; vervolg: QRA en veiligheidsafstanden (tanks tegen containerterrein); N-1-voorraadbeleid kiezen.</t>
         </is>
       </c>
       <c r="F27" s="1" t="n"/>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>DO: graan 30 ha aan de noordkade (masterplan 10) met silo en transportband; RoRo 30 ha op de tweede vinger aan het insteekbekken (masterplan 7/8), ieder een eigen kade van 300 m en eigen inrit.</t>
+          <t>DO: graan 30,4 ha aan de noordkade (masterplan 10) met silo en transportband; RoRo 30,2 ha in de noordoosthoek van vinger 7/8 aan het insteekbekken, ieder een eigen kade van 300 m en eigen poort.</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>DO: fase 1 bij de ingang (C1-C2), kade groeit zuidwaarts; bekkens gebaggerd 184,2 / 210,2 / 236,2 ha; reserve-insteek en hoofdbekken-west (96,8 ha) pas in fase 4.</t>
+          <t>DO: fase 1 aan de noordkop van de containervinger (C1-C2), kade groeit zuidwaarts het insteekbekken in; bekkens gebaggerd 113,9 / 136,9 / 159,9 ha; hoofdbekken west en tweede insteek (157,9 ha) in fase 4.</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>DO: reservering 52,5 ha in de zuidelijke energiezone; gasleiding naar het regionale net; koelwaterinlaat in de voorhaven, uitlaat buiten de zuidelijke dam (indicatief).</t>
+          <t>DO: reservering 47,1 ha in de zuidelijke energiezone; gasleiding naar het regionale net; koelwaterinlaat in de voorhaven, uitlaat buiten de zuidelijke dam (indicatief).</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>DO: hoofdweg + spoor aan de westzijde (zoals de ringweg in het masterplan), takken achter de percelen: noord (graan), midden (RoRo), zuid (containers, LNG, centrale); aparte poorten.</t>
+          <t>DO: zoals de render: hoofdweg en spoor langs de noordrand, ontsluitingsweg aan de westzijde en een ringweg om de vingers langs het tankpark; containers, RoRo, LNG en centrale vanaf de ringweg, graan en havendiensten vanaf de noordweg.</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Havenbekken 3.122.965 m2, geul buiten de mond 2.200.000 m2, terreinophoging 3.019.000 m2 ingevuld; ontwerpbodem als LandXML-oppervlak voor Civil 3D.</t>
+          <t>Havenbekken 2.649.198 m2, geul buiten de mond 2.200.000 m2, terreinophoging 3.266.194 m2 ingevuld; ontwerpbodem als LandXML-oppervlak voor Civil 3D.</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11700</v>
+        <v>11727</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>87</v>
+        <v>646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1700</v>
+        <v>1727</v>
       </c>
       <c r="D11" t="n">
         <v>1670</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>800</v>
+        <v>802.1921820131856</v>
       </c>
       <c r="D13" t="n">
         <v>800</v>
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1200</v>
+        <v>1203.288273019332</v>
       </c>
       <c r="D14" t="n">
         <v>1200</v>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1600</v>
+        <v>1604.384364026371</v>
       </c>
       <c r="D15" t="n">
         <v>1600</v>
@@ -15175,7 +15175,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30</v>
+        <v>30.4</v>
       </c>
       <c r="D20" t="n">
         <v>30</v>
@@ -15231,7 +15231,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="D22" t="n">
         <v>30</v>
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>939</v>
+        <v>729</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>465</v>
+        <v>296</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>31.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>52.5</v>
+        <v>47.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.4</v>
+        <v>43</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
@@ -15405,7 +15405,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>237.8</v>
+        <v>850.2</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
@@ -15426,7 +15426,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>407</v>
+        <v>479</v>
       </c>
       <c r="D30" t="n">
         <v>220</v>
@@ -15450,7 +15450,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1842500</v>
+        <v>1138629</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -15467,7 +15467,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2102500</v>
+        <v>1369033</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2362500</v>
+        <v>1599438</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>760465</v>
+        <v>1049760</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3122965</v>
+        <v>2649198</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3019000</v>
+        <v>3266194</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kustpunt havenas (waterlijn)</t>
+          <t>Referentiepunt kust (render 812,5 / 275)</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -15649,16 +15649,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>297451.11</v>
+        <v>297352.65</v>
       </c>
       <c r="D41" t="n">
-        <v>7649991.36</v>
+        <v>7649661.36</v>
       </c>
       <c r="E41" t="n">
-        <v>-21.2404426</v>
+        <v>-21.2434116</v>
       </c>
       <c r="F41" t="n">
-        <v>-40.9517825</v>
+        <v>-40.95277</v>
       </c>
     </row>
     <row r="42">
@@ -15673,16 +15673,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>298876.85</v>
+        <v>299054.7</v>
       </c>
       <c r="D42" t="n">
-        <v>7649065.48</v>
+        <v>7649370.46</v>
       </c>
       <c r="E42" t="n">
-        <v>-21.2489619</v>
+        <v>-21.2462275</v>
       </c>
       <c r="F42" t="n">
-        <v>-40.9381592</v>
+        <v>-40.9364101</v>
       </c>
     </row>
     <row r="43">
@@ -15697,16 +15697,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>300134.86</v>
+        <v>300533.26</v>
       </c>
       <c r="D43" t="n">
-        <v>7648248.52</v>
+        <v>7649117.76</v>
       </c>
       <c r="E43" t="n">
-        <v>-21.2564782</v>
+        <v>-21.2486725</v>
       </c>
       <c r="F43" t="n">
-        <v>-40.9261374</v>
+        <v>-40.9221977</v>
       </c>
     </row>
     <row r="44">
@@ -15721,16 +15721,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>307263.56</v>
+        <v>308911.77</v>
       </c>
       <c r="D44" t="n">
-        <v>7643619.09</v>
+        <v>7647685.81</v>
       </c>
       <c r="E44" t="n">
-        <v>-21.2990555</v>
+        <v>-21.262505</v>
       </c>
       <c r="F44" t="n">
-        <v>-40.8579896</v>
+        <v>-40.8416497</v>
       </c>
     </row>
     <row r="45">
@@ -15745,16 +15745,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>297737.85</v>
+        <v>297202.27</v>
       </c>
       <c r="D45" t="n">
-        <v>7651802.52</v>
+        <v>7650918.75</v>
       </c>
       <c r="E45" t="n">
-        <v>-21.2241196</v>
+        <v>-21.2320404</v>
       </c>
       <c r="F45" t="n">
-        <v>-40.9488056</v>
+        <v>-40.9540689</v>
       </c>
     </row>
     <row r="46">
@@ -15769,16 +15769,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>296314.32</v>
+        <v>296285.1</v>
       </c>
       <c r="D46" t="n">
-        <v>7648329.97</v>
+        <v>7647740.85</v>
       </c>
       <c r="E46" t="n">
-        <v>-21.255318</v>
+        <v>-21.2606345</v>
       </c>
       <c r="F46" t="n">
-        <v>-40.9629306</v>
+        <v>-40.9632826</v>
       </c>
     </row>
     <row r="47">
@@ -15793,16 +15793,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>297135.17</v>
+        <v>295982.49</v>
       </c>
       <c r="D47" t="n">
-        <v>7650585.23</v>
+        <v>7649572.61</v>
       </c>
       <c r="E47" t="n">
-        <v>-21.2350446</v>
+        <v>-21.2440597</v>
       </c>
       <c r="F47" t="n">
-        <v>-40.9547548</v>
+        <v>-40.9659781</v>
       </c>
     </row>
     <row r="48">
@@ -15817,16 +15817,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>296587.94</v>
+        <v>295525.07</v>
       </c>
       <c r="D48" t="n">
-        <v>7649081.73</v>
+        <v>7648034.81</v>
       </c>
       <c r="E48" t="n">
-        <v>-21.2485603</v>
+        <v>-21.2578946</v>
       </c>
       <c r="F48" t="n">
-        <v>-40.960205</v>
+        <v>-40.9705687</v>
       </c>
     </row>
     <row r="49">
@@ -15837,20 +15837,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Midden LNG-ligplaats</t>
+          <t>LNG-steigerkop</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>297377.21</v>
+        <v>298268.67</v>
       </c>
       <c r="D49" t="n">
-        <v>7648560.34</v>
+        <v>7648742.76</v>
       </c>
       <c r="E49" t="n">
-        <v>-21.2533567</v>
+        <v>-21.2518087</v>
       </c>
       <c r="F49" t="n">
-        <v>-40.9526645</v>
+        <v>-40.9440557</v>
       </c>
     </row>
     <row r="50">
@@ -15865,16 +15865,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>296729.58</v>
+        <v>296296.46</v>
       </c>
       <c r="D50" t="n">
-        <v>7651371.36</v>
+        <v>7650045.75</v>
       </c>
       <c r="E50" t="n">
-        <v>-21.2279005</v>
+        <v>-21.2398224</v>
       </c>
       <c r="F50" t="n">
-        <v>-40.9585675</v>
+        <v>-40.9628973</v>
       </c>
     </row>
     <row r="51">
@@ -15889,16 +15889,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>295815.28</v>
+        <v>295265.72</v>
       </c>
       <c r="D51" t="n">
-        <v>7650906.01</v>
+        <v>7649177.72</v>
       </c>
       <c r="E51" t="n">
-        <v>-21.2320002</v>
+        <v>-21.2475449</v>
       </c>
       <c r="F51" t="n">
-        <v>-40.9674288</v>
+        <v>-40.9729295</v>
       </c>
     </row>
   </sheetData>

--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>11727</v>
+        <v>19720</v>
       </c>
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>DO-tekening: 10.000 m buiten de mond (eindpunt A5 nog op -18,2 m MLWS-lijn leggen) + 1.727 m mond-draaikom</t>
+          <t>DO-tekening: 18.000 m buiten de mond (eindpunt A5 nog op -18,2 m MLWS-lijn leggen) + 1.720 m mond-draaikom</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="C6" s="43" t="n">
-        <v>2649198</v>
+        <v>2151343</v>
       </c>
       <c r="D6" s="35" t="n"/>
       <c r="E6" s="32">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>DO: geul buiten de mond totaal 2.200.000 m2 (220 x 10.000 m); splitsen op DHN -15 m-contour.</t>
+          <t>DO: geul buiten de mond totaal 3.960.000 m2 (220 x 18.000 m); splitsen op DHN -15 m-contour.</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>3266194</v>
+        <v>3232056</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Havenvorm</t>
+          <t>Havenvorm en programma</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>DO: de Porto Central-render is op schaal overgetrokken (10,035 m per pixel, op de kust gedraaid): gebogen dammen met ingang naar het OZO, hoofdbekken oost-west langs de noordkade, schuine vingers en insteekbekkens evenwijdig aan de kust, containervinger (6) met de kraankade aan de insteekzijde, tankpark langs de zuidrand (9) en LNG-steiger bij de zuidelijke dam (18). Zie blad DO-05.</t>
+          <t>DO: de vorm van Porto Central is aangehouden (gebogen dammen, ingang naar het OZO, hoofdbekken langs de noordkade, containervinger, tankpark langs de zuidrand), maar er staan alleen functies uit de opdracht in: containers, droge bulk (graan), voertuigen (RoRo), LNG en de centrale. Erts, werf, industrie, supply base, olie en het tweede insteekbekken zijn weggelaten.</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B02; vervolg: Olie- en droge-bulksteigers (4, 5), werf (3) en erts (2) vallen buiten het programma: weggelaten of reserve.</t>
+          <t>Besluitenlijst B02; vervolg: Geen; eventuele latere uitbreiding apart onderbouwen.</t>
         </is>
       </c>
       <c r="F23" s="1" t="n"/>
@@ -13637,12 +13637,12 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Draaikom en stopweg</t>
+          <t>Manoeuvreren met grote schepen</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>DO: draaikom in de voorhaven op de plaats van de -20 m-cirkel in de render; stopweg 1.727 m = 5,2 LOA; 646 m vrij van afgemeerde schepen en 230 m van kades/dammen.</t>
+          <t>DO: containerkade aan de oostzijde van de vinger, direct aan de voorhaven. Schepen zwaaien in de draaikom (D 720 m = 2,2 LOA) en verhalen zijwaarts met sleepboten naar de kade: geen bocht buiten de draaikom. Graan- en RoRo-schepen varen met een koerswijziging van 19 gr het hoofdbekken in en verlaten het achteruit of zwaaien vooraf in de draaikom. Draaikom 170 m vrij van afgemeerde schepen; stopweg 1.720 m = 5,1 LOA.</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B04; vervolg: Nautische (simulator)toets: bocht van de toegang naar het insteekbekken (ca. 115 gr) met sleepboten.</t>
+          <t>Besluitenlijst B04; vervolg: Toetsen met bochtstralen uit PIANC WG121 en een nautische simulatie met sleepboten.</t>
         </is>
       </c>
       <c r="F25" s="1" t="n"/>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>DO: rechte geul 220 m, -18,20 m MLWS, in het verlengde van de havenmond; koppelpunt 1.500 m buiten de mond (A4). Lengte buiten de mond voorlopig 10.000 m.</t>
+          <t>DO: rechte geul 220 m, -18,20 m MLWS, in het verlengde van de havenmond; koppelpunt 1.500 m buiten de mond (A4). Lengte buiten de mond voorlopig 18.000 m: Porto Central meldt een toegang van ca. 26 km tot ca. -25 m; bij een vergelijkbare helling ligt de -18,2 m-lijn rond 18 km.</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>DO: LNG-tanks in het oostelijke deel van het tankpark (masterplan 9), 296 m van het containerterrein met de ringweg ertussen; LNG-steiger (18) 729 m vrij van de draaikom; ruimte voor een 4e tank.</t>
+          <t>DO: tanks in het zuidelijke deel van de LNG-zone, 296 m van het containerterrein met de zuidweg ertussen; LNG-steiger achter de zuidelijke dam, 561 m vrij van de draaikom; ruimte voor een 4e tank.</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B06; vervolg: QRA en veiligheidsafstanden (tanks tegen containerterrein); N-1-voorraadbeleid kiezen.</t>
+          <t>Besluitenlijst B06; vervolg: QRA en veiligheidsafstanden; N-1-voorraadbeleid kiezen.</t>
         </is>
       </c>
       <c r="F27" s="1" t="n"/>
@@ -13727,12 +13727,12 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Graan en RoRo</t>
+          <t>Droge bulk (graan) en RoRo</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>DO: graan 30,4 ha aan de noordkade (masterplan 10) met silo en transportband; RoRo 30,2 ha in de noordoosthoek van vinger 7/8 aan het insteekbekken, ieder een eigen kade van 300 m en eigen poort.</t>
+          <t>DO: graan 30,4 ha en RoRo 30,4 ha naast elkaar aan de noordkade van het hoofdbekken, ieder een kade van 300 m, eigen poort aan de noordweg; graansilo met transportband, RoRo-ramp.</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B07; vervolg: Ramp- en rijcircuit RoRo en conveyorroute graan detailleren.</t>
+          <t>Besluitenlijst B07; vervolg: Rijcircuit RoRo en conveyorroute graan detailleren.</t>
         </is>
       </c>
       <c r="F28" s="1" t="n"/>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>DO: fase 1 aan de noordkop van de containervinger (C1-C2), kade groeit zuidwaarts het insteekbekken in; bekkens gebaggerd 113,9 / 136,9 / 159,9 ha; hoofdbekken west en tweede insteek (157,9 ha) in fase 4.</t>
+          <t>DO: fase 1 aan de noordkop (C1-C2), de kade groeit zuidwaarts langs de voorhaven; gebaggerd 87,0 / 100,7 / 114,3 ha (hoofdbekken + ligplaatsstroken).</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B08; vervolg: Bouwmethode uitbreiding naast werkende kade (damwand/kistdam) uitwerken.</t>
+          <t>Besluitenlijst B08; vervolg: Bouwmethode uitbreiding naast werkende kade uitwerken.</t>
         </is>
       </c>
       <c r="F29" s="1" t="n"/>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>DO: reservering 47,1 ha in de zuidelijke energiezone; gasleiding naar het regionale net; koelwaterinlaat in de voorhaven, uitlaat buiten de zuidelijke dam (indicatief).</t>
+          <t>DO: reservering 43,5 ha naast de LNG-zone langs de zuidrand; gasleiding naar het regionale net; koelwater indicatief.</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B09; vervolg: Vermogen/proceskeuze vaststellen; recirculatie en temperatuur koelwater toetsen.</t>
+          <t>Besluitenlijst B09; vervolg: Vermogen/proceskeuze vaststellen; recirculatie koelwater toetsen.</t>
         </is>
       </c>
       <c r="F30" s="1" t="n"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>DO: zoals de render: hoofdweg en spoor langs de noordrand, ontsluitingsweg aan de westzijde en een ringweg om de vingers langs het tankpark; containers, RoRo, LNG en centrale vanaf de ringweg, graan en havendiensten vanaf de noordweg.</t>
+          <t>DO: noordweg langs graan, RoRo en havendienst; zuidweg langs containerterrein, LNG en centrale; beide aangesloten op het regionale net aan de westzijde, met spoor.</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Havenbekken 2.649.198 m2, geul buiten de mond 2.200.000 m2, terreinophoging 3.266.194 m2 ingevuld; ontwerpbodem als LandXML-oppervlak voor Civil 3D.</t>
+          <t>Havenbekken 2.151.343 m2, geul buiten de mond 3.960.000 m2, terreinophoging 3.232.056 m2 ingevuld; ontwerpbodem als LandXML-oppervlak voor Civil 3D.</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -14650,7 +14650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -14768,7 +14768,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11727</v>
+        <v>19720</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>646</v>
+        <v>170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1727</v>
+        <v>1720</v>
       </c>
       <c r="D11" t="n">
         <v>1670</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>802.1921820131856</v>
+        <v>802.1921820132022</v>
       </c>
       <c r="D13" t="n">
         <v>800</v>
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1203.288273019332</v>
+        <v>1203.288273019349</v>
       </c>
       <c r="D14" t="n">
         <v>1200</v>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1604.384364026371</v>
+        <v>1604.384364026388</v>
       </c>
       <c r="D15" t="n">
         <v>1600</v>
@@ -15231,7 +15231,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="D22" t="n">
         <v>30</v>
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>729</v>
+        <v>561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47.1</v>
+        <v>43.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -15396,52 +15396,48 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Reserveterreinen</t>
+          <t>Vrije breedte hoofdbekken met schip aan de kade</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>850.2</v>
+        <v>329</v>
+      </c>
+      <c r="D29" t="n">
+        <v>220</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vrije breedte insteekbekken met RoRo-schip</t>
+          <t>Binnenbekken gebaggerd fase 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>479</v>
-      </c>
-      <c r="D30" t="n">
-        <v>220</v>
+        <v>869756</v>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>voldoet</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 1</t>
+          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -15450,7 +15446,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1138629</v>
+        <v>1006559</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -15458,7 +15454,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
+          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -15467,7 +15463,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1369033</v>
+        <v>1143362</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -15475,7 +15471,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
+          <t>Voorhaven + LNG-insteek gebaggerd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -15484,7 +15480,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1599438</v>
+        <v>1007981</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -15492,7 +15488,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Voorhaven + LNG-insteek gebaggerd</t>
+          <t>Havenbekken totaal (zone 1)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15501,15 +15497,23 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1049760</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+        <v>2151343</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Grondwerk C6</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ingevuld</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Havenbekken totaal (zone 1)</t>
+          <t>Geul buiten de mond (zone 2 + 3)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15518,23 +15522,23 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2649198</v>
+        <v>3960000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grondwerk C6</t>
+          <t>Grondwerk C7 + C8</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ingevuld</t>
+          <t>splitsing open</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Geul buiten de mond (zone 2 + 3)</t>
+          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15543,362 +15547,337 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2200000</v>
+        <v>3232056</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grondwerk C7 + C8</t>
+          <t>Grondwerk D21</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>splitsing open</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>3266194</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Grondwerk D21</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
           <t>ingevuld</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Punt</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Omschrijving</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>E (m)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N (m)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Lat</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lon</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Punt</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Omschrijving</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>E (m)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>N (m)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Lon</t>
-        </is>
+          <t>Referentiepunt kust (render 812,5 / 275)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>297135</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7650000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-21.2403293</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-40.9548262</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Referentiepunt kust (render 812,5 / 275)</t>
+          <t>Middelpunt vrije draaikom</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>297135</v>
+        <v>297534.6</v>
       </c>
       <c r="D40" t="n">
-        <v>7650000</v>
+        <v>7649611.92</v>
       </c>
       <c r="E40" t="n">
-        <v>-21.2403293</v>
+        <v>-21.2438783</v>
       </c>
       <c r="F40" t="n">
-        <v>-40.9548262</v>
+        <v>-40.9510234</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Middelpunt vrije draaikom</t>
+          <t>Midden havenmond</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>297352.65</v>
+        <v>299233.15</v>
       </c>
       <c r="D41" t="n">
-        <v>7649661.36</v>
+        <v>7649340.79</v>
       </c>
       <c r="E41" t="n">
-        <v>-21.2434116</v>
+        <v>-21.2465152</v>
       </c>
       <c r="F41" t="n">
-        <v>-40.95277</v>
+        <v>-40.9346946</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Midden havenmond</t>
+          <t>Sleepbootkoppelpunt</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>299054.7</v>
+        <v>300714.4</v>
       </c>
       <c r="D42" t="n">
-        <v>7649370.46</v>
+        <v>7649104.35</v>
       </c>
       <c r="E42" t="n">
-        <v>-21.2462275</v>
+        <v>-21.2488135</v>
       </c>
       <c r="F42" t="n">
-        <v>-40.9364101</v>
+        <v>-40.9204543</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sleepbootkoppelpunt</t>
+          <t>Eindpunt geul (voorlopig)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>300533.26</v>
+        <v>317008.13</v>
       </c>
       <c r="D43" t="n">
-        <v>7649117.76</v>
+        <v>7646503.5</v>
       </c>
       <c r="E43" t="n">
-        <v>-21.2486725</v>
+        <v>-21.274017</v>
       </c>
       <c r="F43" t="n">
-        <v>-40.9221977</v>
+        <v>-40.7637753</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Eindpunt geul (voorlopig)</t>
+          <t>Wortel noordelijke golfbreker</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>308911.77</v>
+        <v>297202.27</v>
       </c>
       <c r="D44" t="n">
-        <v>7647685.81</v>
+        <v>7650918.75</v>
       </c>
       <c r="E44" t="n">
-        <v>-21.262505</v>
+        <v>-21.2320404</v>
       </c>
       <c r="F44" t="n">
-        <v>-40.8416497</v>
+        <v>-40.9540689</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wortel noordelijke golfbreker</t>
+          <t>Wortel zuidelijke golfbreker</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>297202.27</v>
+        <v>296285.1</v>
       </c>
       <c r="D45" t="n">
-        <v>7650918.75</v>
+        <v>7647740.85</v>
       </c>
       <c r="E45" t="n">
-        <v>-21.2320404</v>
+        <v>-21.2606345</v>
       </c>
       <c r="F45" t="n">
-        <v>-40.9540689</v>
+        <v>-40.9632826</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wortel zuidelijke golfbreker</t>
+          <t>Containerkade noordeinde</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>296285.1</v>
+        <v>296970.74</v>
       </c>
       <c r="D46" t="n">
-        <v>7647740.85</v>
+        <v>7649746.86</v>
       </c>
       <c r="E46" t="n">
-        <v>-21.2606345</v>
+        <v>-21.2425969</v>
       </c>
       <c r="F46" t="n">
-        <v>-40.9632826</v>
+        <v>-40.9564384</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Containerkade noordeinde (F1)</t>
+          <t>Containerkade zuideinde</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>295982.49</v>
+        <v>296513.33</v>
       </c>
       <c r="D47" t="n">
-        <v>7649572.61</v>
+        <v>7648209.06</v>
       </c>
       <c r="E47" t="n">
-        <v>-21.2440597</v>
+        <v>-21.2564321</v>
       </c>
       <c r="F47" t="n">
-        <v>-40.9659781</v>
+        <v>-40.9610281</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Containerkade zuideinde (F3)</t>
+          <t>LNG-steigerkop</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>295525.07</v>
+        <v>298268.67</v>
       </c>
       <c r="D48" t="n">
-        <v>7648034.81</v>
+        <v>7648742.76</v>
       </c>
       <c r="E48" t="n">
-        <v>-21.2578946</v>
+        <v>-21.2518087</v>
       </c>
       <c r="F48" t="n">
-        <v>-40.9705687</v>
+        <v>-40.9440557</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LNG-steigerkop</t>
+          <t>Graankade midden</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>298268.67</v>
+        <v>296296.46</v>
       </c>
       <c r="D49" t="n">
-        <v>7648742.76</v>
+        <v>7650045.75</v>
       </c>
       <c r="E49" t="n">
-        <v>-21.2518087</v>
+        <v>-21.2398224</v>
       </c>
       <c r="F49" t="n">
-        <v>-40.9440557</v>
+        <v>-40.9628973</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Graankade midden</t>
+          <t>RoRo-kade midden</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>296296.46</v>
+        <v>295762.81</v>
       </c>
       <c r="D50" t="n">
-        <v>7650045.75</v>
+        <v>7649951.65</v>
       </c>
       <c r="E50" t="n">
-        <v>-21.2398224</v>
+        <v>-21.2406122</v>
       </c>
       <c r="F50" t="n">
-        <v>-40.9628973</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>A12</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>RoRo-kade midden</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>295265.72</v>
-      </c>
-      <c r="D51" t="n">
-        <v>7649177.72</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-21.2475449</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-40.9729295</v>
+        <v>-40.9680487</v>
       </c>
     </row>
   </sheetData>

--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="C6" s="43" t="n">
-        <v>2151343</v>
+        <v>2606110</v>
       </c>
       <c r="D6" s="35" t="n"/>
       <c r="E6" s="32">
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>3232056</v>
+        <v>3229941</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>DO: de vorm van Porto Central is aangehouden (gebogen dammen, ingang naar het OZO, hoofdbekken langs de noordkade, containervinger, tankpark langs de zuidrand), maar er staan alleen functies uit de opdracht in: containers, droge bulk (graan), voertuigen (RoRo), LNG en de centrale. Erts, werf, industrie, supply base, olie en het tweede insteekbekken zijn weggelaten.</t>
+          <t>DO: de vorm van de render blijft: gebogen dammen, ingang naar het OZO, hoofdbekken langs de noordkade, twee schuine vingers met insteekbekkens en het tankpark langs de zuidrand. Er staan alleen functies uit de opdracht in: containers (vinger 6), droge bulk/graan (noordkade), voertuigen/RoRo (vinger 7/8), LNG en de centrale (zuidrand). Erts, werf, industrie en olie zijn weggelaten; de overige ruimte op vinger 7/8 en de tweede insteek zijn uitbreidingsruimte voor de eigen ladingstromen na 2045.</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B02; vervolg: Geen; eventuele latere uitbreiding apart onderbouwen.</t>
+          <t>Besluitenlijst B02; vervolg: Uitbreidingsruimte apart onderbouwen als de groei na 2045 aan de orde komt.</t>
         </is>
       </c>
       <c r="F23" s="1" t="n"/>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>DO: containerkade aan de oostzijde van de vinger, direct aan de voorhaven. Schepen zwaaien in de draaikom (D 720 m = 2,2 LOA) en verhalen zijwaarts met sleepboten naar de kade: geen bocht buiten de draaikom. Graan- en RoRo-schepen varen met een koerswijziging van 19 gr het hoofdbekken in en verlaten het achteruit of zwaaien vooraf in de draaikom. Draaikom 170 m vrij van afgemeerde schepen; stopweg 1.720 m = 5,1 LOA.</t>
+          <t>DO: containerkade aan de voorhavenzijde van vinger 6: containerschepen zwaaien in de draaikom (D 720 m = 2,2 LOA) en verhalen zijwaarts met sleepboten naar de kade, zonder bocht buiten de draaikom. Graan- en RoRo-schepen (ca. 230 m) varen met 19 gr koerswijziging het hoofdbekken in en zwaaien in een draaikom binnenhaven van D 460 m (2 x LOA) op de kruising met het insteekbekken, op de plaats van de -16 m-cirkel in de render; die ligt 286 m vrij van afgemeerde schepen. Draaikom voorhaven 170 m vrij; stopweg 1.720 m = 5,1 LOA.</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>DO: graan 30,4 ha en RoRo 30,4 ha naast elkaar aan de noordkade van het hoofdbekken, ieder een kade van 300 m, eigen poort aan de noordweg; graansilo met transportband, RoRo-ramp.</t>
+          <t>DO: graan 30,4 ha aan de noordkade (render 10) met silo en transportband; RoRo 30,2 ha in de noordoosthoek van vinger 7/8 met kade aan het insteekbekken; ieder een kade van 300 m en een eigen poort.</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>DO: fase 1 aan de noordkop (C1-C2), de kade groeit zuidwaarts langs de voorhaven; gebaggerd 87,0 / 100,7 / 114,3 ha (hoofdbekken + ligplaatsstroken).</t>
+          <t>DO: containers fase 1 aan de noordkop (C1-C2), de kade groeit zuidwaarts langs de voorhaven; gebaggerd 132,5 / 146,1 / 159,8 ha; insteek zuid, hoofdbekken west en tweede insteek (178,8 ha) pas na 2045.</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -13882,7 +13882,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Havenbekken 2.151.343 m2, geul buiten de mond 3.960.000 m2, terreinophoging 3.232.056 m2 ingevuld; ontwerpbodem als LandXML-oppervlak voor Civil 3D.</t>
+          <t>Havenbekken 2.606.110 m2, geul buiten de mond 3.960.000 m2, terreinophoging 3.229.941 m2 ingevuld; ontwerpbodem als LandXML-oppervlak voor Civil 3D.</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -14650,7 +14650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -15231,7 +15231,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="D22" t="n">
         <v>30</v>
@@ -15250,7 +15250,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LNG-ligplaatsenvelop</t>
+          <t>Draaikom binnenhaven (graan/RoRo)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -15259,26 +15259,26 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="D23" t="n">
-        <v>400</v>
+        <v>458</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>tekenbrief</t>
+          <t>2 x LOA graan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>dolphins indicatief</t>
+          <t>vrij getoetst</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LNG-envelop tot draaikom</t>
+          <t xml:space="preserve">  afstand tot afgemeerde schepen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -15287,7 +15287,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>561</v>
+        <v>286</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -15297,14 +15297,14 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>vrij; QRA volgt</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LNG-tanks tot containerterrein</t>
+          <t>LNG-ligplaatsenvelop</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -15313,69 +15313,73 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>296</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="D25" t="n">
+        <v>400</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>tekenbrief</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>QRA volgt</t>
+          <t>dolphins indicatief</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LNG-zone (tanks + hervergassing)</t>
+          <t>LNG-envelop tot draaikom</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Invoer D51-D52</t>
-        </is>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3 tanks + optie 4e</t>
+          <t>vrij; QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Centrale + utilities (reservering)</t>
+          <t>LNG-tanks tot containerterrein</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>geen vast oppervlak</t>
-        </is>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Havendiensten / sleepboten</t>
+          <t>LNG-zone (tanks + hervergassing)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -15384,77 +15388,93 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>43</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+        <v>31.9</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Invoer D51-D52</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>3 tanks + optie 4e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vrije breedte hoofdbekken met schip aan de kade</t>
+          <t>Centrale + utilities (reservering)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>329</v>
-      </c>
-      <c r="D29" t="n">
-        <v>220</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>43.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>geen vast oppervlak</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>reservering</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 1</t>
+          <t>Havendiensten / sleepboten</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>869756</v>
+        <v>43</v>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>reservering</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
+          <t>Vrije breedte hoofdbekken met graanschip aan de kade</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1006559</v>
+        <v>334</v>
+      </c>
+      <c r="D31" t="n">
+        <v>220</v>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>voldoet</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
+          <t>Binnenbekken gebaggerd fase 1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -15463,7 +15483,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1143362</v>
+        <v>1324523</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -15471,7 +15491,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Voorhaven + LNG-insteek gebaggerd</t>
+          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -15480,7 +15500,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1007981</v>
+        <v>1461326</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -15488,7 +15508,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Havenbekken totaal (zone 1)</t>
+          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15497,23 +15517,15 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2151343</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Grondwerk C6</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ingevuld</t>
-        </is>
-      </c>
+        <v>1598128</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Geul buiten de mond (zone 2 + 3)</t>
+          <t>Voorhaven + LNG-insteek gebaggerd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15522,23 +15534,15 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3960000</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Grondwerk C7 + C8</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>splitsing open</t>
-        </is>
-      </c>
+        <v>1007981</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
+          <t>Havenbekken totaal (zone 1)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15547,337 +15551,411 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3232056</v>
+        <v>2606110</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grondwerk D21</t>
+          <t>Grondwerk C6</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>ingevuld</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Geul buiten de mond (zone 2 + 3)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3960000</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Grondwerk C7 + C8</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>splitsing open</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Punt</t>
+          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Omschrijving</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>E (m)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>N (m)</t>
-        </is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3229941</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lat</t>
+          <t>Grondwerk D21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lon</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Referentiepunt kust (render 812,5 / 275)</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>297135</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7650000</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-21.2403293</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-40.9548262</v>
+          <t>ingevuld</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>Punt</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Middelpunt vrije draaikom</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>297534.6</v>
-      </c>
-      <c r="D40" t="n">
-        <v>7649611.92</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-21.2438783</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-40.9510234</v>
+          <t>Omschrijving</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>E (m)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>N (m)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Lat</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lon</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Midden havenmond</t>
+          <t>Referentiepunt kust (render 812,5 / 275)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>299233.15</v>
+        <v>297135</v>
       </c>
       <c r="D41" t="n">
-        <v>7649340.79</v>
+        <v>7650000</v>
       </c>
       <c r="E41" t="n">
-        <v>-21.2465152</v>
+        <v>-21.2403293</v>
       </c>
       <c r="F41" t="n">
-        <v>-40.9346946</v>
+        <v>-40.9548262</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sleepbootkoppelpunt</t>
+          <t>Middelpunt vrije draaikom</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>300714.4</v>
+        <v>297534.6</v>
       </c>
       <c r="D42" t="n">
-        <v>7649104.35</v>
+        <v>7649611.92</v>
       </c>
       <c r="E42" t="n">
-        <v>-21.2488135</v>
+        <v>-21.2438783</v>
       </c>
       <c r="F42" t="n">
-        <v>-40.9204543</v>
+        <v>-40.9510234</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eindpunt geul (voorlopig)</t>
+          <t>Midden havenmond</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>317008.13</v>
+        <v>299233.15</v>
       </c>
       <c r="D43" t="n">
-        <v>7646503.5</v>
+        <v>7649340.79</v>
       </c>
       <c r="E43" t="n">
-        <v>-21.274017</v>
+        <v>-21.2465152</v>
       </c>
       <c r="F43" t="n">
-        <v>-40.7637753</v>
+        <v>-40.9346946</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wortel noordelijke golfbreker</t>
+          <t>Sleepbootkoppelpunt</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>297202.27</v>
+        <v>300714.4</v>
       </c>
       <c r="D44" t="n">
-        <v>7650918.75</v>
+        <v>7649104.35</v>
       </c>
       <c r="E44" t="n">
-        <v>-21.2320404</v>
+        <v>-21.2488135</v>
       </c>
       <c r="F44" t="n">
-        <v>-40.9540689</v>
+        <v>-40.9204543</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wortel zuidelijke golfbreker</t>
+          <t>Eindpunt geul (voorlopig)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>296285.1</v>
+        <v>317008.13</v>
       </c>
       <c r="D45" t="n">
-        <v>7647740.85</v>
+        <v>7646503.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-21.2606345</v>
+        <v>-21.274017</v>
       </c>
       <c r="F45" t="n">
-        <v>-40.9632826</v>
+        <v>-40.7637753</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Containerkade noordeinde</t>
+          <t>Wortel noordelijke golfbreker</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>296970.74</v>
+        <v>297202.27</v>
       </c>
       <c r="D46" t="n">
-        <v>7649746.86</v>
+        <v>7650918.75</v>
       </c>
       <c r="E46" t="n">
-        <v>-21.2425969</v>
+        <v>-21.2320404</v>
       </c>
       <c r="F46" t="n">
-        <v>-40.9564384</v>
+        <v>-40.9540689</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Containerkade zuideinde</t>
+          <t>Wortel zuidelijke golfbreker</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>296513.33</v>
+        <v>296285.1</v>
       </c>
       <c r="D47" t="n">
-        <v>7648209.06</v>
+        <v>7647740.85</v>
       </c>
       <c r="E47" t="n">
-        <v>-21.2564321</v>
+        <v>-21.2606345</v>
       </c>
       <c r="F47" t="n">
-        <v>-40.9610281</v>
+        <v>-40.9632826</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LNG-steigerkop</t>
+          <t>Containerkade noordeinde</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>298268.67</v>
+        <v>296970.74</v>
       </c>
       <c r="D48" t="n">
-        <v>7648742.76</v>
+        <v>7649746.86</v>
       </c>
       <c r="E48" t="n">
-        <v>-21.2518087</v>
+        <v>-21.2425969</v>
       </c>
       <c r="F48" t="n">
-        <v>-40.9440557</v>
+        <v>-40.9564384</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Graankade midden</t>
+          <t>Containerkade zuideinde</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>296296.46</v>
+        <v>296513.33</v>
       </c>
       <c r="D49" t="n">
-        <v>7650045.75</v>
+        <v>7648209.06</v>
       </c>
       <c r="E49" t="n">
-        <v>-21.2398224</v>
+        <v>-21.2564321</v>
       </c>
       <c r="F49" t="n">
-        <v>-40.9628973</v>
+        <v>-40.9610281</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LNG-steigerkop</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>298268.67</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7648742.76</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-21.2518087</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-40.9440557</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Graankade midden</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>296296.46</v>
+      </c>
+      <c r="D51" t="n">
+        <v>7650045.75</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-21.2398224</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-40.9628973</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>A12</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>RoRo-kade midden</t>
         </is>
       </c>
-      <c r="C50" t="n">
-        <v>295762.81</v>
-      </c>
-      <c r="D50" t="n">
-        <v>7649951.65</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-21.2406122</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-40.9680487</v>
+      <c r="C52" t="n">
+        <v>295265.72</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7649177.72</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-21.2475449</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-40.9729295</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Middelpunt draaikom binnenhaven</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>295694.75</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7649644.15</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-21.2433813</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-40.968741</v>
       </c>
     </row>
   </sheetData>

--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -14650,7 +14650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -15429,42 +15429,57 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Havendiensten / sleepboten</t>
+          <t>STS-kranen F1 / F2 / F3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ha</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>43</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6 / 12 / 20</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6 / 12 / 20</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Containers D19-F19</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>gelijk</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vrije breedte hoofdbekken met graanschip aan de kade</t>
+          <t>TEU-grondslots stackzone F3 (28 m2/slot)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>slots</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>334</v>
+        <v>40558</v>
       </c>
       <c r="D31" t="n">
-        <v>220</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>40444</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Containers F25</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>voldoet</t>
@@ -15474,125 +15489,164 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 1</t>
+          <t>Stackzone bruto</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1324523</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+        <v>113.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Containers F26</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>voldoet</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
+          <t>Graansilo's 8 x D 30 m x 40 m</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1461326</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+        <v>169646</v>
+      </c>
+      <c r="D33" t="n">
+        <v>154100</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Overige terminals F9</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>voldoet</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
+          <t>RoRo-parkeercapaciteit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>auto's</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1598128</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+        <v>9698</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7479</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Overige terminals F15</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>voldoet</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Voorhaven + LNG-insteek gebaggerd</t>
+          <t>Centrale STEG-eenheden</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1007981</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+        <v>2260</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2256</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Overige terminals F30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>rekenvoorbeeld</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Havenbekken totaal (zone 1)</t>
+          <t>Havendiensten / sleepboten</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2606110</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Grondwerk C6</t>
-        </is>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ingevuld</t>
+          <t>reservering</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Geul buiten de mond (zone 2 + 3)</t>
+          <t>Vrije breedte hoofdbekken met graanschip aan de kade</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3960000</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Grondwerk C7 + C8</t>
-        </is>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="D37" t="n">
+        <v>220</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>splitsing open</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
+          <t>Binnenbekken gebaggerd fase 1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -15601,360 +15655,478 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3229941</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Grondwerk D21</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>ingevuld</t>
-        </is>
-      </c>
+        <v>1324523</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1461326</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Punt</t>
+          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Omschrijving</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>E (m)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>N (m)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Lon</t>
-        </is>
-      </c>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1598128</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Voorhaven + LNG-insteek gebaggerd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Referentiepunt kust (render 812,5 / 275)</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>297135</v>
-      </c>
-      <c r="D41" t="n">
-        <v>7650000</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-21.2403293</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-40.9548262</v>
-      </c>
+        <v>1007981</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>Havenbekken totaal (zone 1)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Middelpunt vrije draaikom</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>297534.6</v>
-      </c>
-      <c r="D42" t="n">
-        <v>7649611.92</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-21.2438783</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-40.9510234</v>
+        <v>2606110</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Grondwerk C6</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ingevuld</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>Geul buiten de mond (zone 2 + 3)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Midden havenmond</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>299233.15</v>
-      </c>
-      <c r="D43" t="n">
-        <v>7649340.79</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-21.2465152</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-40.9346946</v>
+        <v>3960000</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Grondwerk C7 + C8</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>splitsing open</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sleepbootkoppelpunt</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>300714.4</v>
-      </c>
-      <c r="D44" t="n">
-        <v>7649104.35</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-21.2488135</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-40.9204543</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Eindpunt geul (voorlopig)</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>317008.13</v>
-      </c>
-      <c r="D45" t="n">
-        <v>7646503.5</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-21.274017</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-40.7637753</v>
+        <v>3229941</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Grondwerk D21</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ingevuld</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>Punt</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wortel noordelijke golfbreker</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>297202.27</v>
-      </c>
-      <c r="D46" t="n">
-        <v>7650918.75</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-21.2320404</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-40.9540689</v>
+          <t>Omschrijving</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>E (m)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>N (m)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Lat</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Lon</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wortel zuidelijke golfbreker</t>
+          <t>Referentiepunt kust (render 812,5 / 275)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>296285.1</v>
+        <v>297135</v>
       </c>
       <c r="D47" t="n">
-        <v>7647740.85</v>
+        <v>7650000</v>
       </c>
       <c r="E47" t="n">
-        <v>-21.2606345</v>
+        <v>-21.2403293</v>
       </c>
       <c r="F47" t="n">
-        <v>-40.9632826</v>
+        <v>-40.9548262</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Containerkade noordeinde</t>
+          <t>Middelpunt vrije draaikom</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>296970.74</v>
+        <v>297534.6</v>
       </c>
       <c r="D48" t="n">
-        <v>7649746.86</v>
+        <v>7649611.92</v>
       </c>
       <c r="E48" t="n">
-        <v>-21.2425969</v>
+        <v>-21.2438783</v>
       </c>
       <c r="F48" t="n">
-        <v>-40.9564384</v>
+        <v>-40.9510234</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Containerkade zuideinde</t>
+          <t>Midden havenmond</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>296513.33</v>
+        <v>299233.15</v>
       </c>
       <c r="D49" t="n">
-        <v>7648209.06</v>
+        <v>7649340.79</v>
       </c>
       <c r="E49" t="n">
-        <v>-21.2564321</v>
+        <v>-21.2465152</v>
       </c>
       <c r="F49" t="n">
-        <v>-40.9610281</v>
+        <v>-40.9346946</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LNG-steigerkop</t>
+          <t>Sleepbootkoppelpunt</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>298268.67</v>
+        <v>300714.4</v>
       </c>
       <c r="D50" t="n">
-        <v>7648742.76</v>
+        <v>7649104.35</v>
       </c>
       <c r="E50" t="n">
-        <v>-21.2518087</v>
+        <v>-21.2488135</v>
       </c>
       <c r="F50" t="n">
-        <v>-40.9440557</v>
+        <v>-40.9204543</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Graankade midden</t>
+          <t>Eindpunt geul (voorlopig)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>296296.46</v>
+        <v>317008.13</v>
       </c>
       <c r="D51" t="n">
-        <v>7650045.75</v>
+        <v>7646503.5</v>
       </c>
       <c r="E51" t="n">
-        <v>-21.2398224</v>
+        <v>-21.274017</v>
       </c>
       <c r="F51" t="n">
-        <v>-40.9628973</v>
+        <v>-40.7637753</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RoRo-kade midden</t>
+          <t>Wortel noordelijke golfbreker</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>295265.72</v>
+        <v>297202.27</v>
       </c>
       <c r="D52" t="n">
-        <v>7649177.72</v>
+        <v>7650918.75</v>
       </c>
       <c r="E52" t="n">
-        <v>-21.2475449</v>
+        <v>-21.2320404</v>
       </c>
       <c r="F52" t="n">
-        <v>-40.9729295</v>
+        <v>-40.9540689</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Wortel zuidelijke golfbreker</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>296285.1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7647740.85</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-21.2606345</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-40.9632826</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Containerkade noordeinde</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>296970.74</v>
+      </c>
+      <c r="D54" t="n">
+        <v>7649746.86</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-21.2425969</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-40.9564384</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Containerkade zuideinde</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>296513.33</v>
+      </c>
+      <c r="D55" t="n">
+        <v>7648209.06</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-21.2564321</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-40.9610281</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LNG-steigerkop</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>298268.67</v>
+      </c>
+      <c r="D56" t="n">
+        <v>7648742.76</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-21.2518087</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-40.9440557</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Graankade midden</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>296296.46</v>
+      </c>
+      <c r="D57" t="n">
+        <v>7650045.75</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-21.2398224</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-40.9628973</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RoRo-kade midden</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>295265.72</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7649177.72</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-21.2475449</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-40.9729295</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>A13</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Middelpunt draaikom binnenhaven</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C59" t="n">
         <v>295694.75</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D59" t="n">
         <v>7649644.15</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E59" t="n">
         <v>-21.2433813</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F59" t="n">
         <v>-40.968741</v>
       </c>
     </row>

--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -5931,18 +5931,18 @@
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>19720</v>
+        <v>36720</v>
       </c>
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>VOORLOPIG</t>
+          <t>GEBCO 2026</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>DO-tekening: 18.000 m buiten de mond (eindpunt A5 nog op -18,2 m MLWS-lijn leggen) + 1.720 m mond-draaikom</t>
+          <t>DO-tekening: 35.000 m buiten de mond (natuurlijk -18,2 m MLWS volgens GEBCO 2026, geen peiling) + 1.720 m mond-draaikom</t>
         </is>
       </c>
     </row>
@@ -10480,9 +10480,11 @@
         </is>
       </c>
       <c r="C6" s="43" t="n">
-        <v>2606110</v>
-      </c>
-      <c r="D6" s="35" t="n"/>
+        <v>2781000</v>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>-3.3</v>
+      </c>
       <c r="E6" s="32">
         <f>Nautiek!D25</f>
         <v/>
@@ -10497,7 +10499,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>DO: binnenbekken F1-F3 + voorhaven + LNG-insteek (gesloten vlakken, Maatstaat). Bestaande diepte nog invullen.</t>
+          <t>DO: bekkens + voorhaven, bodemmodel GEBCO 2026 + Copernicus DEM (negatief = boven MLWS, land wordt ontgraven). Celmethode met dieptezones (-18,20/-16,20/-13,70): 59.054.405 m3</t>
         </is>
       </c>
     </row>
@@ -10510,8 +10512,12 @@
           <t>Geul tot DHN -15m</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="35" t="n"/>
+      <c r="C7" s="43" t="n">
+        <v>5280300</v>
+      </c>
+      <c r="D7" s="38" t="n">
+        <v>12.54</v>
+      </c>
       <c r="E7" s="32">
         <f>Nautiek!D25</f>
         <v/>
@@ -10526,7 +10532,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>DO: geul buiten de mond totaal 3.960.000 m2 (220 x 18.000 m); splitsen op DHN -15 m-contour.</t>
+          <t>DO: geul vanaf de mond tot de natuurlijke -15 m-lijn (24.000 m), 220 m breed; celmethode 29.904.700 m3</t>
         </is>
       </c>
     </row>
@@ -10539,8 +10545,12 @@
           <t>Geul voorbij DHN -15m</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="35" t="n"/>
+      <c r="C8" s="43" t="n">
+        <v>2418300</v>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>17.09</v>
+      </c>
       <c r="E8" s="32">
         <f>Nautiek!D25</f>
         <v/>
@@ -10555,7 +10565,7 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>Zie H7; oppervlak pas invullen na splitsing op de dieptelijn.</t>
+          <t>DO: geul van de -15 m-lijn tot het geuleinde (35.000 m); celmethode 3.570.530 m3</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10830,7 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>3229941</v>
+        <v>3274200</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
@@ -10851,9 +10861,15 @@
           <t>m t.o.v. datum</t>
         </is>
       </c>
-      <c r="D22" s="35" t="n"/>
+      <c r="D22" s="38" t="n">
+        <v>7.17</v>
+      </c>
       <c r="E22" s="32" t="n"/>
-      <c r="F22" s="32" t="n"/>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>Copernicus DEM GLO-30 (oppervlak incl. begroeiing) t.o.v. MLWS: overschat het maaiveld.</t>
+        </is>
+      </c>
       <c r="G22" s="13" t="n"/>
       <c r="H22" s="13" t="n"/>
     </row>
@@ -10873,9 +10889,15 @@
           <t>m zelfde datum</t>
         </is>
       </c>
-      <c r="D23" s="35" t="n"/>
+      <c r="D23" s="38" t="n">
+        <v>5</v>
+      </c>
       <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>Aanname: terrein op +5,0 m MLWS (boven springtij + golfoploop, te toetsen).</t>
+        </is>
+      </c>
       <c r="G23" s="13" t="n"/>
       <c r="H23" s="13" t="n"/>
     </row>
@@ -10895,9 +10917,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D24" s="35" t="n"/>
+      <c r="D24" s="38" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>Aanname. Celmethode: ophoging 154.096 m3, afgraving 7.173.117 m3 (terrein ligt grotendeels hoger dan +5,0 m).</t>
+        </is>
+      </c>
       <c r="G24" s="13" t="n"/>
       <c r="H24" s="13" t="n"/>
     </row>
@@ -13642,7 +13670,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>DO: containerkade aan de voorhavenzijde van vinger 6: containerschepen zwaaien in de draaikom (D 720 m = 2,2 LOA) en verhalen zijwaarts met sleepboten naar de kade, zonder bocht buiten de draaikom. Graan- en RoRo-schepen (ca. 230 m) varen met 19 gr koerswijziging het hoofdbekken in en zwaaien in een draaikom binnenhaven van D 460 m (2 x LOA) op de kruising met het insteekbekken, op de plaats van de -16 m-cirkel in de render; die ligt 286 m vrij van afgemeerde schepen. Draaikom voorhaven 170 m vrij; stopweg 1.720 m = 5,1 LOA.</t>
+          <t>DO: containerkade aan de westzijde van vinger 6, in het insteekbekken. Golftoets (DO-09): aan de oostzijde (voorhaven) wordt Hs 1,66 m (grens 0,5 m), in de insteek 0,01 m. Containerschepen varen met sleepboten door de draaikom (D 720 m) het hoofdbekken in, zwaaien op de zwaaiplaats binnenhaven (D 500 m = 1,5 LOA, met sleepboten; het hoofdbekken is daar verbreed) en worden achteruit de insteek in gesleept, zodat ze met de kop naar buiten afmeren. De zwaaiplaats ligt 165 m vrij van afgemeerde schepen en 91 m van de oever. Draaikom voorhaven 416 m vrij; stopweg 1.720 m = 5,1 LOA.</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -13672,7 +13700,7 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>DO: rechte geul 220 m, -18,20 m MLWS, in het verlengde van de havenmond; koppelpunt 1.500 m buiten de mond (A4). Lengte buiten de mond voorlopig 18.000 m: Porto Central meldt een toegang van ca. 26 km tot ca. -25 m; bij een vergelijkbare helling ligt de -18,2 m-lijn rond 18 km.</t>
+          <t>DO: rechte geul 220 m, -18,20 m MLWS, in het verlengde van de havenmond; koppelpunt 1.500 m buiten de mond (A4). Bodemmodel uit GEBCO 2026 + Copernicus DEM (DO-10): het kustplateau is vlak (-13 tot -17 m); de natuurlijke bodem is pas op 35.000 m overal dieper dan -18,2 m MLWS (-15 m op 24.000 m). Geul daarom 35 km lang; zone 2/3 gesplitst op de -15 m-lijn.</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -13682,7 +13710,7 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B05; vervolg: Eindpunt op de -18,2 m MLWS-dieptelijn van de bathymetrie leggen; MLWS-DHN koppelen; geullengte terugzetten in Nautiek D31.</t>
+          <t>Besluitenlijst B05; vervolg: Multibeampeiling langs het tracé; MLWS-DHN koppelen; geul eventueel gefaseerd (eerst -15,5 m, getijvenster).</t>
         </is>
       </c>
       <c r="F26" s="1" t="n"/>
@@ -13702,7 +13730,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>DO: tanks in het zuidelijke deel van de LNG-zone, 296 m van het containerterrein met de zuidweg ertussen; LNG-steiger achter de zuidelijke dam, 561 m vrij van de draaikom; ruimte voor een 4e tank.</t>
+          <t>DO: LNG-steiger achter het midden van de zuidelijke dam (golftoets Hs 0,90 m &lt; 1,0 m; bij de havenmond 1,08 m). Tanks oostelijk in de LNG-zone: cryogene leiding ca. 1,4 km. Veiligheidszone 250 m rond schip/steiger en rond de tanks, nautische controlezone 500 m (Hong Kong LNG-terminal; literatuur 250-750 m): geen andere schepen of gebouwen in de 250 m-zones; draaikom 626 m buiten de zone, containerterrein 46 m buiten de tankzone. Ligplaats en vaarweg -16,20 m MLWS.</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -13712,7 +13740,7 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B06; vervolg: QRA en veiligheidsafstanden; N-1-voorraadbeleid kiezen.</t>
+          <t>Besluitenlijst B06; vervolg: QRA (plaatsgebonden en groepsrisico) en definitieve zones; N-1-voorraadbeleid kiezen.</t>
         </is>
       </c>
       <c r="F27" s="1" t="n"/>
@@ -13762,7 +13790,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>DO: containers fase 1 aan de noordkop (C1-C2), de kade groeit zuidwaarts langs de voorhaven; gebaggerd 132,5 / 146,1 / 159,8 ha; insteek zuid, hoofdbekken west en tweede insteek (178,8 ha) pas na 2045.</t>
+          <t>DO: containers fase 1 aan de noordkop (C1-C2), de kade groeit zuidwaarts langs de westzijde van vinger 6; gebaggerd 118,9 / 141,9 / 165,0 ha; insteek zuid, hoofdbekken west en tweede insteek (122,1 ha) pas na 2045.</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -13882,17 +13910,17 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Havenbekken 2.606.110 m2, geul buiten de mond 3.960.000 m2, terreinophoging 3.229.941 m2 ingevuld; ontwerpbodem als LandXML-oppervlak voor Civil 3D.</t>
+          <t>Celmethode (30 m) op het bodemmodel: zone 1 59,1, zone 2 29,9, zone 3 3,6 mln m3 (totaal 92,5 mln m3). Dieptezones per scheepstype (diepgang + 3,7 m): containers/graan -18,20, LNG -16,20, RoRo -13,70 m MLWS; besparing 0,75 mln m3. Ontwerpbodem per dieptezone als LandXML-oppervlak voor Civil 3D.</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>Deels open</t>
+          <t>Indicatief</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>Besluitenlijst B12; vervolg: Bathymetrie als Civil 3D-oppervlak inlezen en volume tegen Ontwerpbodem_DO berekenen; geul splitsen op DHN -15 m.</t>
+          <t>Besluitenlijst B12; vervolg: Na peiling herberekenen (Volumes Dashboard); grondsoorten uit boringen.</t>
         </is>
       </c>
       <c r="F33" s="1" t="n"/>
@@ -14650,7 +14678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -14768,7 +14796,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18000</v>
+        <v>35000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -14777,7 +14805,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VOORLOPIG</t>
+          <t>GEBCO, geen peiling</t>
         </is>
       </c>
     </row>
@@ -14793,7 +14821,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19720</v>
+        <v>36720</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -14802,14 +14830,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VOORLOPIG</t>
+          <t>GEBCO, geen peiling</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vrije draaikom diameter</t>
+          <t>Vrije draaikom voorhaven diameter</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14846,7 +14874,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>170</v>
+        <v>416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -14872,7 +14900,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>220</v>
+        <v>397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -14979,7 +15007,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>802.1921820132022</v>
+        <v>802.1921820131856</v>
       </c>
       <c r="D13" t="n">
         <v>800</v>
@@ -15007,7 +15035,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1203.288273019349</v>
+        <v>1203.288273019332</v>
       </c>
       <c r="D14" t="n">
         <v>1200</v>
@@ -15035,7 +15063,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1604.384364026388</v>
+        <v>1604.384364026371</v>
       </c>
       <c r="D15" t="n">
         <v>1600</v>
@@ -15250,7 +15278,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Draaikom binnenhaven (graan/RoRo)</t>
+          <t>Zwaaiplaats binnenhaven (met sleepboten)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -15259,14 +15287,14 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="D23" t="n">
-        <v>458</v>
+        <v>501</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2 x LOA graan</t>
+          <t>1,5 x LOA container</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -15278,7 +15306,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  afstand tot afgemeerde schepen</t>
+          <t xml:space="preserve">  afstand tot oever</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -15287,7 +15315,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>286</v>
+        <v>91</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -15304,61 +15332,63 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LNG-ligplaatsenvelop</t>
+          <t>Dieptezone LNG-vaarweg en -ligplaats</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m MLWS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>400</v>
+        <v>-16.2</v>
       </c>
       <c r="D25" t="n">
-        <v>400</v>
+        <v>-16.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>tekenbrief</t>
+          <t>diepgang 12,5 + 3,7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>dolphins indicatief</t>
+          <t>bespaart bagger</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LNG-envelop tot draaikom</t>
+          <t>Dieptezone RoRo-ligplaats</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m MLWS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>561</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+        <v>-13.7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>diepgang 10,0 + 3,7</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>vrij; QRA volgt</t>
+          <t>bespaart bagger</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LNG-tanks tot containerterrein</t>
+          <t>Golftoets containers (Hs insteek)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -15367,145 +15397,147 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>296</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DO-09</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>QRA volgt</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LNG-zone (tanks + hervergassing)</t>
+          <t>Golftoets graan (Hs)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31.9</v>
+        <v>0.73</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Invoer D51-D52</t>
+          <t>DO-09</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3 tanks + optie 4e</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Centrale + utilities (reservering)</t>
+          <t>Golftoets RoRo (Hs)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>43.5</v>
+        <v>0.03</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>geen vast oppervlak</t>
+          <t>DO-09</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STS-kranen F1 / F2 / F3</t>
+          <t>Golftoets LNG (Hs)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>st</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>6 / 12 / 20</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>6 / 12 / 20</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Containers D19-F19</t>
+          <t>DO-09</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>gelijk</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TEU-grondslots stackzone F3 (28 m2/slot)</t>
+          <t>LNG cryogene leiding</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>slots</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>40558</v>
-      </c>
-      <c r="D31" t="n">
-        <v>40444</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Containers F25</t>
-        </is>
-      </c>
+        <v>1353</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>ingekort</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Stackzone bruto</t>
+          <t>Schepen in LNG-zone 250 m</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>st</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>113.6</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>113.2</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Containers F26</t>
+          <t>Hong Kong LNG annex</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -15517,53 +15549,49 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Graansilo's 8 x D 30 m x 40 m</t>
+          <t>Containerterrein tot tankzone 250 m</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>169646</v>
-      </c>
-      <c r="D33" t="n">
-        <v>154100</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Overige terminals F9</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>voldoet; QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RoRo-parkeercapaciteit</t>
+          <t xml:space="preserve">  afstand tot afgemeerde schepen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>auto's</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9698</v>
-      </c>
-      <c r="D34" t="n">
-        <v>7479</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Overige terminals F15</t>
-        </is>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>voldoet</t>
@@ -15573,56 +15601,61 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Centrale STEG-eenheden</t>
+          <t>LNG-ligplaatsenvelop</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2260</v>
+        <v>400</v>
       </c>
       <c r="D35" t="n">
-        <v>2256</v>
+        <v>400</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Overige terminals F30</t>
+          <t>tekenbrief</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>rekenvoorbeeld</t>
+          <t>dolphins indicatief</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Havendiensten / sleepboten</t>
+          <t>LNG-envelop tot draaikom</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>43</v>
+        <v>876</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>vrij; QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vrije breedte hoofdbekken met graanschip aan de kade</t>
+          <t>LNG-tanks tot containerterrein</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -15631,503 +15664,794 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>334</v>
-      </c>
-      <c r="D37" t="n">
-        <v>220</v>
+        <v>296</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 1</t>
+          <t>LNG-zone (tanks + hervergassing)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1324523</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+        <v>36.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Invoer D51-D52</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3 tanks + optie 4e</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
+          <t>Centrale + utilities (reservering)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1461326</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+        <v>43.5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>geen vast oppervlak</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>reservering</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
+          <t>STS-kranen F1 / F2 / F3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1598128</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6 / 12 / 20</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6 / 12 / 20</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Containers D19-F19</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>gelijk</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Voorhaven + LNG-insteek gebaggerd</t>
+          <t>TEU-grondslots stackzone F3 (28 m2/slot)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>slots</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1007981</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+        <v>40558</v>
+      </c>
+      <c r="D41" t="n">
+        <v>40444</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Containers F25</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>voldoet</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Havenbekken totaal (zone 1)</t>
+          <t>Stackzone bruto</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2606110</v>
+        <v>113.6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>113.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grondwerk C6</t>
+          <t>Containers F26</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ingevuld</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Geul buiten de mond (zone 2 + 3)</t>
+          <t>Graansilo's 8 x D 30 m x 40 m</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3960000</v>
+        <v>169646</v>
+      </c>
+      <c r="D43" t="n">
+        <v>154100</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Grondwerk C7 + C8</t>
+          <t>Overige terminals F9</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>splitsing open</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
+          <t>RoRo-parkeercapaciteit</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>auto's</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3229941</v>
+        <v>9698</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7479</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grondwerk D21</t>
+          <t>Overige terminals F15</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ingevuld</t>
+          <t>voldoet</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Centrale STEG-eenheden</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2260</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2256</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Overige terminals F30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>rekenvoorbeeld</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Punt</t>
+          <t>Havendiensten / sleepboten</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Omschrijving</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>E (m)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>N (m)</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Lat</t>
-        </is>
-      </c>
+          <t>ha</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>43</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lon</t>
+          <t>reservering</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>Vrije breedte hoofdbekken met graanschip aan de kade</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Referentiepunt kust (render 812,5 / 275)</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>297135</v>
+        <v>334</v>
       </c>
       <c r="D47" t="n">
-        <v>7650000</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-21.2403293</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-40.9548262</v>
+        <v>220</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>voldoet</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>Binnenbekken gebaggerd fase 1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Middelpunt vrije draaikom</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>297534.6</v>
-      </c>
-      <c r="D48" t="n">
-        <v>7649611.92</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-21.2438783</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-40.9510234</v>
-      </c>
+        <v>1189081</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Midden havenmond</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>299233.15</v>
-      </c>
-      <c r="D49" t="n">
-        <v>7649340.79</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-21.2465152</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-40.9346946</v>
-      </c>
+        <v>1419486</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sleepbootkoppelpunt</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>300714.4</v>
-      </c>
-      <c r="D50" t="n">
-        <v>7649104.35</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-21.2488135</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-40.9204543</v>
-      </c>
+        <v>1649890</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>Voorhaven + LNG-insteek gebaggerd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Eindpunt geul (voorlopig)</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>317008.13</v>
-      </c>
-      <c r="D51" t="n">
-        <v>7646503.5</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-21.274017</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-40.7637753</v>
-      </c>
+        <v>1132971</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>Havenbekken totaal (zone 1)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wortel noordelijke golfbreker</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>297202.27</v>
-      </c>
-      <c r="D52" t="n">
-        <v>7650918.75</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-21.2320404</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-40.9540689</v>
+        <v>2782861</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Grondwerk C6</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ingevuld</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>Geul buiten de mond (zone 2 + 3)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wortel zuidelijke golfbreker</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>296285.1</v>
-      </c>
-      <c r="D53" t="n">
-        <v>7647740.85</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-21.2606345</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-40.9632826</v>
+        <v>7700000</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Grondwerk C7 + C8</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>gesplitst op -15 m</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>Baggervolume zone 1 / 2 / 3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Containerkade noordeinde</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>296970.74</v>
-      </c>
-      <c r="D54" t="n">
-        <v>7649746.86</v>
-      </c>
-      <c r="E54" t="n">
-        <v>-21.2425969</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-40.9564384</v>
+          <t>mln m3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>59,1 / 29,9 / 3,6</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Grondwerk F6-F8</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>celmethode, indicatief</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Containerkade zuideinde</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>296513.33</v>
-      </c>
-      <c r="D55" t="n">
-        <v>7648209.06</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-21.2564321</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-40.9610281</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>LNG-steigerkop</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>298268.67</v>
-      </c>
-      <c r="D56" t="n">
-        <v>7648742.76</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-21.2518087</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-40.9440557</v>
+        <v>3273444</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Grondwerk D21</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ingevuld</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>Punt</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Graankade midden</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>296296.46</v>
-      </c>
-      <c r="D57" t="n">
-        <v>7650045.75</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-21.2398224</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-40.9628973</v>
+          <t>Omschrijving</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>E (m)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>N (m)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Lat</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lon</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RoRo-kade midden</t>
+          <t>Referentiepunt kust (render 812,5 / 275)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>295265.72</v>
+        <v>297135</v>
       </c>
       <c r="D58" t="n">
-        <v>7649177.72</v>
+        <v>7650000</v>
       </c>
       <c r="E58" t="n">
-        <v>-21.2475449</v>
+        <v>-21.2403293</v>
       </c>
       <c r="F58" t="n">
-        <v>-40.9729295</v>
+        <v>-40.9548262</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Middelpunt vrije draaikom</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>297534.6</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7649611.92</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-21.2438783</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-40.9510234</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Midden havenmond</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>299233.15</v>
+      </c>
+      <c r="D60" t="n">
+        <v>7649340.79</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-21.2465152</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-40.9346946</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sleepbootkoppelpunt</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>300714.4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>7649104.35</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-21.2488135</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-40.9204543</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Eindpunt geul (voorlopig)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>333795.61</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7643823.84</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-21.2998354</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-40.602281</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Wortel noordelijke golfbreker</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>297202.27</v>
+      </c>
+      <c r="D63" t="n">
+        <v>7650918.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-21.2320404</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-40.9540689</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Wortel zuidelijke golfbreker</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>296285.1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7647740.85</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-21.2606345</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-40.9632826</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Containerkade noordeinde</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>295982.49</v>
+      </c>
+      <c r="D65" t="n">
+        <v>7649572.61</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-21.2440597</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-40.9659781</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Containerkade zuideinde</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>295525.07</v>
+      </c>
+      <c r="D66" t="n">
+        <v>7648034.81</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-21.2578946</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-40.9705687</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LNG-steigerkop</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>297643.11</v>
+      </c>
+      <c r="D67" t="n">
+        <v>7648245.24</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-21.2562317</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-40.9501407</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Graankade midden</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>296296.46</v>
+      </c>
+      <c r="D68" t="n">
+        <v>7650045.75</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-21.2398224</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-40.9628973</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RoRo-kade midden</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>295265.72</v>
+      </c>
+      <c r="D69" t="n">
+        <v>7649177.72</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-21.2475449</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-40.9729295</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>A13</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Middelpunt draaikom binnenhaven</t>
         </is>
       </c>
-      <c r="C59" t="n">
-        <v>295694.75</v>
-      </c>
-      <c r="D59" t="n">
-        <v>7649644.15</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-21.2433813</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-40.968741</v>
+      <c r="C70" t="n">
+        <v>295569.79</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7649774.96</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-21.242186</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-40.969929</v>
       </c>
     </row>
   </sheetData>

--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="D31" s="38" t="n">
-        <v>36720</v>
+        <v>21946</v>
       </c>
       <c r="E31" s="32" t="n"/>
       <c r="F31" s="32" t="n"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>DO-tekening: 35.000 m buiten de mond (natuurlijk -18,2 m MLWS volgens GEBCO 2026, geen peiling) + 1.720 m mond-draaikom</t>
+          <t>DO-tekening: 20.225 m buiten de mond (natuurlijk -18,2 m MLWS volgens GEBCO 2026, geen peiling) + 1.720 m mond-draaikom</t>
         </is>
       </c>
     </row>
@@ -10480,10 +10480,10 @@
         </is>
       </c>
       <c r="C6" s="43" t="n">
-        <v>2781000</v>
+        <v>2930400</v>
       </c>
       <c r="D6" s="38" t="n">
-        <v>-3.3</v>
+        <v>-3.23</v>
       </c>
       <c r="E6" s="32">
         <f>Nautiek!D25</f>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>DO: bekkens + voorhaven, bodemmodel GEBCO 2026 + Copernicus DEM (negatief = boven MLWS, land wordt ontgraven). Celmethode met dieptezones (-18,20/-16,20/-13,70): 59.054.405 m3</t>
+          <t>DO: bekkens + voorhaven, bodemmodel GEBCO 2026 + Copernicus DEM (negatief = boven MLWS, land wordt ontgraven). Celmethode met dieptezones (-18,20/-16,20/-13,70): 61.936.560 m3</t>
         </is>
       </c>
     </row>
@@ -10513,10 +10513,10 @@
         </is>
       </c>
       <c r="C7" s="43" t="n">
-        <v>5280300</v>
+        <v>3898800</v>
       </c>
       <c r="D7" s="38" t="n">
-        <v>12.54</v>
+        <v>13.51</v>
       </c>
       <c r="E7" s="32">
         <f>Nautiek!D25</f>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>DO: geul vanaf de mond tot de natuurlijke -15 m-lijn (24.000 m), 220 m breed; celmethode 29.904.700 m3</t>
+          <t>DO: geul vanaf de mond tot de natuurlijke -15 m-lijn (17.250 m), 220 m breed; celmethode 18.280.082 m3</t>
         </is>
       </c>
     </row>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="C8" s="43" t="n">
-        <v>2418300</v>
+        <v>657000</v>
       </c>
       <c r="D8" s="38" t="n">
-        <v>17.09</v>
+        <v>16.71</v>
       </c>
       <c r="E8" s="32">
         <f>Nautiek!D25</f>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>DO: geul van de -15 m-lijn tot het geuleinde (35.000 m); celmethode 3.570.530 m3</t>
+          <t>DO: geul van de -15 m-lijn tot het geuleinde (20.225 m); celmethode 1.233.306 m3</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
         </is>
       </c>
       <c r="D21" s="38" t="n">
-        <v>3274200</v>
+        <v>3459600</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         </is>
       </c>
       <c r="D22" s="38" t="n">
-        <v>7.17</v>
+        <v>7.06</v>
       </c>
       <c r="E22" s="32" t="n"/>
       <c r="F22" s="32" t="inlineStr">
@@ -10923,7 +10923,7 @@
       <c r="E24" s="32" t="n"/>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>Aanname. Celmethode: ophoging 154.096 m3, afgraving 7.173.117 m3 (terrein ligt grotendeels hoger dan +5,0 m).</t>
+          <t>Aanname. Celmethode: ophoging 354.822 m3, afgraving 7.346.330 m3 (terrein ligt grotendeels hoger dan +5,0 m).</t>
         </is>
       </c>
       <c r="G24" s="13" t="n"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>DO: containerkade aan de westzijde van vinger 6, in het insteekbekken. Golftoets (DO-09): aan de oostzijde (voorhaven) wordt Hs 1,66 m (grens 0,5 m), in de insteek 0,01 m. Containerschepen varen met sleepboten door de draaikom (D 720 m) het hoofdbekken in, zwaaien op de zwaaiplaats binnenhaven (D 500 m = 1,5 LOA, met sleepboten; het hoofdbekken is daar verbreed) en worden achteruit de insteek in gesleept, zodat ze met de kop naar buiten afmeren. De zwaaiplaats ligt 165 m vrij van afgemeerde schepen en 91 m van de oever. Draaikom voorhaven 416 m vrij; stopweg 1.720 m = 5,1 LOA.</t>
+          <t>DO: containerkade aan de westzijde van vinger 6, in het insteekbekken. Golftoets (DO-09): aan de oostzijde (voorhaven) wordt Hs 2,08 m (grens 0,5 m), in de insteek 0,24 m. Containerschepen varen met sleepboten door de draaikom (D 720 m) het hoofdbekken in, zwaaien op de zwaaiplaats binnenhaven (D 670 m = 2 x LOA van het maatgevende containerschip; het hoofdbekken is daar verbreed, zodat de draai zonder krappe marges lukt) en worden achteruit de insteek in gesleept, zodat ze met de kop naar buiten afmeren. De zwaaiplaats ligt 115 m vrij van afgemeerde schepen en 156 m van de oever. Draaikom voorhaven 416 m vrij; stopweg 1.720 m = 5,1 LOA.</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>DO: rechte geul 220 m, -18,20 m MLWS, in het verlengde van de havenmond; koppelpunt 1.500 m buiten de mond (A4). Bodemmodel uit GEBCO 2026 + Copernicus DEM (DO-10): het kustplateau is vlak (-13 tot -17 m); de natuurlijke bodem is pas op 35.000 m overal dieper dan -18,2 m MLWS (-15 m op 24.000 m). Geul daarom 35 km lang; zone 2/3 gesplitst op de -15 m-lijn.</t>
+          <t>DO: geul 220 m, -18,20 m MLWS: 2,5 km recht in het verlengde van de havenmond (koppelpunt sleepboten op 1.500 m, A4), dan een bocht met straal 3.400 m (ca. 10 x LOA, verbreed tot 260 m, A14) naar 145 gr en recht tot de natuurlijke -18,2 m MLWS. Bodemmodel GEBCO 2026 + Copernicus DEM (DO-10): naar het ZO is het veel eerder diep. Lengte buiten de mond 20,2 km met 19,5 mln m3 (rechtdoor: 35,0 km, 33,5 mln m3). De haven 1 km verder in zee leggen bespaart ca. 3,3 mln m3 bagger maar kost ca. 0,54 mln m3 extra stortsteen in de dammen: ongeveer kostenneutraal, daarom niet gedaan. Zone 2/3 gesplitst op de -15 m-lijn.</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>DO: LNG-steiger achter het midden van de zuidelijke dam (golftoets Hs 0,90 m &lt; 1,0 m; bij de havenmond 1,08 m). Tanks oostelijk in de LNG-zone: cryogene leiding ca. 1,4 km. Veiligheidszone 250 m rond schip/steiger en rond de tanks, nautische controlezone 500 m (Hong Kong LNG-terminal; literatuur 250-750 m): geen andere schepen of gebouwen in de 250 m-zones; draaikom 626 m buiten de zone, containerterrein 46 m buiten de tankzone. Ligplaats en vaarweg -16,20 m MLWS.</t>
+          <t>DO: LNG-steiger op de gunstigste plek achter de zuidelijke dam (golftoets met reflectie Hs 0,98 m &lt;= 1,0 m; bij de havenmond 1,98 m). Tanks in het zuidelijke deel van de LNG-zone, zodat de 250 m-zone ruim buiten het containerterrein blijft; cryogene leiding ca. 1,2 km. Veiligheidszone 250 m rond schip/steiger en rond de tanks, nautische controlezone 500 m (Hong Kong LNG-terminal; literatuur 250-750 m): geen andere schepen of gebouwen in de 250 m-zones; draaikom 739 m buiten de zone, containerterrein 227 m buiten de tankzone. Ligplaats en vaarweg -16,20 m MLWS.</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>DO: graan 30,4 ha aan de noordkade (render 10) met silo en transportband; RoRo 30,2 ha in de noordoosthoek van vinger 7/8 met kade aan het insteekbekken; ieder een kade van 300 m en een eigen poort.</t>
+          <t>DO: graan 30,4 ha aan de noordkade (render 10) met silo en transportband; de graan- en havendienstkade zijn open kades op palen boven een golfdempend talud (Cr 0,45 i.p.v. 0,9 voor een kademuur; Hs 0,96 m). RoRo 30,2 ha op vinger 7/8 met kade 400 m dieper in de insteek (Hs 0,17 m &lt;= 0,3 m); ieder een kade van 300 m en een eigen poort.</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>DO: containers fase 1 aan de noordkop (C1-C2), de kade groeit zuidwaarts langs de westzijde van vinger 6; gebaggerd 118,9 / 141,9 / 165,0 ha; insteek zuid, hoofdbekken west en tweede insteek (122,1 ha) pas na 2045.</t>
+          <t>DO: containers fase 1 aan de noordkop (C1-C2), de kade groeit zuidwaarts langs de westzijde van vinger 6; gebaggerd 128,8 / 151,0 / 174,1 ha; insteek zuid, hoofdbekken west en tweede insteek (122,1 ha) pas na 2045.</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Celmethode (30 m) op het bodemmodel: zone 1 59,1, zone 2 29,9, zone 3 3,6 mln m3 (totaal 92,5 mln m3). Dieptezones per scheepstype (diepgang + 3,7 m): containers/graan -18,20, LNG -16,20, RoRo -13,70 m MLWS; besparing 0,75 mln m3. Ontwerpbodem per dieptezone als LandXML-oppervlak voor Civil 3D.</t>
+          <t>Celmethode (30 m) op het bodemmodel: zone 1 61,9, zone 2 18,3, zone 3 1,2 mln m3 (totaal 81,4 mln m3). Dieptezones per scheepstype (diepgang + 3,7 m): containers/graan -18,20, LNG -16,20, RoRo -13,70 m MLWS; besparing 0,86 mln m3. Ontwerpbodem per dieptezone als LandXML-oppervlak voor Civil 3D.</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -14678,7 +14678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -14796,7 +14796,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35000</v>
+        <v>20225</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36720</v>
+        <v>21946</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -14865,33 +14865,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Draaikom tot afgemeerde schepen</t>
+          <t>Geul: recht stuk / bochtstraal / richting</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>416</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>m / m / gr</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2.500 / 3.400 / 145</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PIANC WG121 (R &gt;= 5 LOA)</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>bocht 260 m breed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Draaikom tot kades/dammen</t>
+          <t>Geul rechtdoor (variant)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14900,24 +14901,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>397</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>35000</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DO-10</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>afgevallen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Havenmond vrij tussen footprints</t>
+          <t>Draaikom tot afgemeerde schepen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14926,16 +14926,14 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
-      </c>
-      <c r="D10" t="n">
-        <v>350</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Nautiek D29</t>
-        </is>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>voldoet</t>
@@ -14945,7 +14943,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stopweg havenmond - draaikom</t>
+          <t>Draaikom tot kades/dammen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -14954,16 +14952,14 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1720</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1670</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>5 x LOA</t>
-        </is>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>voldoet</t>
@@ -14973,7 +14969,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sleepbootkoppelpunt buiten mond</t>
+          <t>Havenmond vrij tussen footprints</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -14982,23 +14978,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1500</v>
+        <v>350</v>
+      </c>
+      <c r="D12" t="n">
+        <v>350</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>rapport 5.1</t>
+          <t>Nautiek D29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ingetekend</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Containerkade fase 1</t>
+          <t>Stopweg havenmond - draaikom</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -15007,26 +15006,26 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>802.1921820131856</v>
+        <v>1720</v>
       </c>
       <c r="D13" t="n">
-        <v>800</v>
+        <v>1670</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Containers D18</t>
+          <t>5 x LOA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>gelijk</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Containerkade fase 2</t>
+          <t>Sleepbootkoppelpunt buiten mond</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -15035,26 +15034,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1203.288273019332</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Containers E18</t>
+          <t>rapport 5.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>gelijk</t>
+          <t>ingetekend</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Containerkade fase 3</t>
+          <t>Containerkade fase 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -15063,14 +15059,14 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1604.384364026371</v>
+        <v>802.1921820131856</v>
       </c>
       <c r="D15" t="n">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Containers F18</t>
+          <t>Containers D18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -15082,23 +15078,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Containerterrein fase 1</t>
+          <t>Containerkade fase 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>1203.288273019332</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>1200</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Invoer D20 (vraag 40,8)</t>
+          <t>Containers E18</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -15110,23 +15106,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Containerterrein fase 2</t>
+          <t>Containerkade fase 3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>108</v>
+        <v>1604.384364026371</v>
       </c>
       <c r="D17" t="n">
-        <v>108</v>
+        <v>1600</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Invoer E20 (vraag 67,9)</t>
+          <t>Containers F18</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -15138,7 +15134,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Containerterrein fase 3</t>
+          <t>Containerterrein fase 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15147,14 +15143,14 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Invoer F20 (vraag 135,9)</t>
+          <t>Invoer D20 (vraag 40,8)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -15166,23 +15162,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Graankade</t>
+          <t>Containerterrein fase 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>300</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>300</v>
+        <v>108</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>rapport 8.1</t>
+          <t>Invoer E20 (vraag 67,9)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -15194,7 +15190,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Graanterrein</t>
+          <t>Containerterrein fase 3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -15203,14 +15199,14 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30.4</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Invoer D39 (vraag 5,1)</t>
+          <t>Invoer F20 (vraag 135,9)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -15222,7 +15218,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RoRo-kade</t>
+          <t>Graankade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -15238,7 +15234,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>rapport 8.2</t>
+          <t>rapport 8.1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -15250,7 +15246,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RoRo-terrein</t>
+          <t>Graanterrein</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -15259,14 +15255,14 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="D22" t="n">
         <v>30</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Invoer D46 (vraag 26,9)</t>
+          <t>Invoer D39 (vraag 5,1)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -15278,7 +15274,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zwaaiplaats binnenhaven (met sleepboten)</t>
+          <t>RoRo-kade</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -15287,164 +15283,164 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D23" t="n">
-        <v>501</v>
+        <v>300</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1,5 x LOA container</t>
+          <t>rapport 8.2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>vrij getoetst</t>
+          <t>gelijk</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  afstand tot oever</t>
+          <t>RoRo-terrein</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>91</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>30.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Invoer D46 (vraag 26,9)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>gelijk</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dieptezone LNG-vaarweg en -ligplaats</t>
+          <t>Zwaaiplaats binnenhaven</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>m MLWS</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-16.2</v>
+        <v>670</v>
       </c>
       <c r="D25" t="n">
-        <v>-16.2</v>
+        <v>668</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>diepgang 12,5 + 3,7</t>
+          <t>2 x LOA container</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>bespaart bagger</t>
+          <t>vrij getoetst</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dieptezone RoRo-ligplaats</t>
+          <t xml:space="preserve">  afstand tot oever</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>m MLWS</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-13.7</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-13.7</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>diepgang 10,0 + 3,7</t>
-        </is>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>bespaart bagger</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Golftoets containers (Hs insteek)</t>
+          <t>Dieptezone LNG-vaarweg en -ligplaats</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m MLWS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01</v>
+        <v>-16.2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>-16.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DO-09</t>
+          <t>diepgang 12,5 + 3,7</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>bespaart bagger</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Golftoets graan (Hs)</t>
+          <t>Dieptezone RoRo-ligplaats</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m MLWS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.73</v>
+        <v>-13.7</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>-13.7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DO-09</t>
+          <t>diepgang 10,0 + 3,7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>bespaart bagger</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Golftoets RoRo (Hs)</t>
+          <t>Golftoets containers (Hs insteek)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -15453,10 +15449,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -15472,7 +15468,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Golftoets LNG (Hs)</t>
+          <t>Golftoets graan (Hs, open kade)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -15481,7 +15477,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -15500,7 +15496,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LNG cryogene leiding</t>
+          <t>Golftoets RoRo (Hs)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -15509,35 +15505,42 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1353</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>0.17</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DO-09</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ingekort</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schepen in LNG-zone 250 m</t>
+          <t>Golftoets LNG (Hs)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>st</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hong Kong LNG annex</t>
+          <t>DO-09</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -15549,7 +15552,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Containerterrein tot tankzone 250 m</t>
+          <t>LNG cryogene leiding</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -15558,40 +15561,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>46</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
+        <v>1223</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>voldoet; QRA volgt</t>
+          <t>ingekort</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  afstand tot afgemeerde schepen</t>
+          <t>Schepen in LNG-zone 250 m</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>st</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>165</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Hong Kong LNG annex</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>voldoet</t>
@@ -15601,7 +15601,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LNG-ligplaatsenvelop</t>
+          <t>Containerterrein tot tankzone 250 m</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15610,26 +15610,24 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>400</v>
-      </c>
-      <c r="D35" t="n">
-        <v>400</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>tekenbrief</t>
-        </is>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>dolphins indicatief</t>
+          <t>voldoet; QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LNG-envelop tot draaikom</t>
+          <t xml:space="preserve">  afstand tot afgemeerde schepen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15638,7 +15636,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>876</v>
+        <v>115</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -15648,14 +15646,14 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>vrij; QRA volgt</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LNG-tanks tot containerterrein</t>
+          <t>LNG-ligplaatsenvelop</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -15664,173 +15662,171 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>296</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="D37" t="n">
+        <v>400</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>tekenbrief</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>QRA volgt</t>
+          <t>dolphins indicatief</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LNG-zone (tanks + hervergassing)</t>
+          <t>LNG-envelop tot draaikom</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Invoer D51-D52</t>
-        </is>
-      </c>
+        <v>989</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3 tanks + optie 4e</t>
+          <t>vrij; QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Centrale + utilities (reservering)</t>
+          <t>LNG-tanks tot containerterrein</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>geen vast oppervlak</t>
-        </is>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>QRA volgt</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STS-kranen F1 / F2 / F3</t>
+          <t>LNG-zone (tanks + hervergassing)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>st</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>6 / 12 / 20</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>6 / 12 / 20</t>
-        </is>
+          <t>ha</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>54.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Containers D19-F19</t>
+          <t>Invoer D51-D52</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>gelijk</t>
+          <t>3 tanks + optie 4e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TEU-grondslots stackzone F3 (28 m2/slot)</t>
+          <t>Centrale + utilities (reservering)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>slots</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40558</v>
-      </c>
-      <c r="D41" t="n">
-        <v>40444</v>
+        <v>43.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Containers F25</t>
+          <t>geen vast oppervlak</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>reservering</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Stackzone bruto</t>
+          <t>STS-kranen F1 / F2 / F3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ha</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>113.6</v>
-      </c>
-      <c r="D42" t="n">
-        <v>113.2</v>
+          <t>st</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6 / 12 / 20</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6 / 12 / 20</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Containers F26</t>
+          <t>Containers D19-F19</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>gelijk</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Graansilo's 8 x D 30 m x 40 m</t>
+          <t>TEU-grondslots stackzone F3 (28 m2/slot)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>slots</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>169646</v>
+        <v>40558</v>
       </c>
       <c r="D43" t="n">
-        <v>154100</v>
+        <v>40444</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Overige terminals F9</t>
+          <t>Containers F25</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -15842,23 +15838,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RoRo-parkeercapaciteit</t>
+          <t>Stackzone bruto</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>auto's</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9698</v>
+        <v>113.6</v>
       </c>
       <c r="D44" t="n">
-        <v>7479</v>
+        <v>113.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Overige terminals F15</t>
+          <t>Containers F26</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -15870,114 +15866,136 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Centrale STEG-eenheden</t>
+          <t>Graansilo's 8 x D 30 m x 40 m</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2260</v>
+        <v>169646</v>
       </c>
       <c r="D45" t="n">
-        <v>2256</v>
+        <v>154100</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Overige terminals F30</t>
+          <t>Overige terminals F9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>rekenvoorbeeld</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Havendiensten / sleepboten</t>
+          <t>RoRo-parkeercapaciteit</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ha</t>
+          <t>auto's</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>43</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>9698</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7479</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Overige terminals F15</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>reservering</t>
+          <t>voldoet</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Vrije breedte hoofdbekken met graanschip aan de kade</t>
+          <t>Centrale STEG-eenheden</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>334</v>
+        <v>2260</v>
       </c>
       <c r="D47" t="n">
-        <v>220</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>2256</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Overige terminals F30</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>voldoet</t>
+          <t>rekenvoorbeeld</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 1</t>
+          <t>Havendiensten / sleepboten</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>ha</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1189081</v>
+        <v>43</v>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>reservering</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
+          <t>Vrije breedte hoofdbekken met graanschip aan de kade</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1419486</v>
+        <v>334</v>
+      </c>
+      <c r="D49" t="n">
+        <v>220</v>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>voldoet</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
+          <t>Binnenbekken gebaggerd fase 1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -15986,7 +16004,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1649890</v>
+        <v>1287977</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -15994,7 +16012,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Voorhaven + LNG-insteek gebaggerd</t>
+          <t>Binnenbekken gebaggerd fase 2 (cumulatief)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -16003,7 +16021,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1132971</v>
+        <v>1510224</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
@@ -16011,7 +16029,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Havenbekken totaal (zone 1)</t>
+          <t>Binnenbekken gebaggerd fase 3 (cumulatief)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -16020,23 +16038,15 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2782861</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Grondwerk C6</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>ingevuld</t>
-        </is>
-      </c>
+        <v>1740629</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Geul buiten de mond (zone 2 + 3)</t>
+          <t>Voorhaven + LNG-insteek gebaggerd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -16045,50 +16055,40 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7700000</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Grondwerk C7 + C8</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>gesplitst op -15 m</t>
-        </is>
-      </c>
+        <v>1188749</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Baggervolume zone 1 / 2 / 3</t>
+          <t>Havenbekken totaal (zone 1)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>mln m3</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>59,1 / 29,9 / 3,6</t>
-        </is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2929377</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grondwerk F6-F8</t>
+          <t>Grondwerk C6</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>celmethode, indicatief</t>
+          <t>ingevuld</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
+          <t>Geul buiten de mond (zone 2 + 3)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -16097,361 +16097,437 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3273444</v>
+        <v>4558615</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grondwerk D21</t>
+          <t>Grondwerk C7 + C8</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ingevuld</t>
+          <t>gesplitst op -15 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Baggervolume zone 1 / 2 / 3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>mln m3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>61,9 / 18,3 / 1,2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Grondwerk F6-F8</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>celmethode, indicatief</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Punt</t>
+          <t>Terreinophoging (terminals, LNG, centrale, havendienst)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Omschrijving</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>E (m)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>N (m)</t>
-        </is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>3459480</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lat</t>
+          <t>Grondwerk D21</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lon</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Referentiepunt kust (render 812,5 / 275)</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>297135</v>
-      </c>
-      <c r="D58" t="n">
-        <v>7650000</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-21.2403293</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-40.9548262</v>
+          <t>ingevuld</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>Punt</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Middelpunt vrije draaikom</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>297534.6</v>
-      </c>
-      <c r="D59" t="n">
-        <v>7649611.92</v>
-      </c>
-      <c r="E59" t="n">
-        <v>-21.2438783</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-40.9510234</v>
+          <t>Omschrijving</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>E (m)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>N (m)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Lat</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lon</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Midden havenmond</t>
+          <t>Referentiepunt kust (render 812,5 / 275)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>299233.15</v>
+        <v>297135</v>
       </c>
       <c r="D60" t="n">
-        <v>7649340.79</v>
+        <v>7650000</v>
       </c>
       <c r="E60" t="n">
-        <v>-21.2465152</v>
+        <v>-21.2403293</v>
       </c>
       <c r="F60" t="n">
-        <v>-40.9346946</v>
+        <v>-40.9548262</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sleepbootkoppelpunt</t>
+          <t>Middelpunt vrije draaikom</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>300714.4</v>
+        <v>297534.6</v>
       </c>
       <c r="D61" t="n">
-        <v>7649104.35</v>
+        <v>7649611.92</v>
       </c>
       <c r="E61" t="n">
-        <v>-21.2488135</v>
+        <v>-21.2438783</v>
       </c>
       <c r="F61" t="n">
-        <v>-40.9204543</v>
+        <v>-40.9510234</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eindpunt geul (voorlopig)</t>
+          <t>Midden havenmond</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>333795.61</v>
+        <v>299233.15</v>
       </c>
       <c r="D62" t="n">
-        <v>7643823.84</v>
+        <v>7649340.79</v>
       </c>
       <c r="E62" t="n">
-        <v>-21.2998354</v>
+        <v>-21.2465152</v>
       </c>
       <c r="F62" t="n">
-        <v>-40.602281</v>
+        <v>-40.9346946</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wortel noordelijke golfbreker</t>
+          <t>Sleepbootkoppelpunt</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>297202.27</v>
+        <v>300714.4</v>
       </c>
       <c r="D63" t="n">
-        <v>7650918.75</v>
+        <v>7649104.35</v>
       </c>
       <c r="E63" t="n">
-        <v>-21.2320404</v>
+        <v>-21.2488135</v>
       </c>
       <c r="F63" t="n">
-        <v>-40.9540689</v>
+        <v>-40.9204543</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wortel zuidelijke golfbreker</t>
+          <t>Eindpunt geul (natuurlijk -18,2 m)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>296285.1</v>
+        <v>312554.73</v>
       </c>
       <c r="D64" t="n">
-        <v>7647740.85</v>
+        <v>7635252.11</v>
       </c>
       <c r="E64" t="n">
-        <v>-21.2606345</v>
+        <v>-21.3751711</v>
       </c>
       <c r="F64" t="n">
-        <v>-40.9632826</v>
+        <v>-40.8079279</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Containerkade noordeinde</t>
+          <t>Wortel noordelijke golfbreker</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>295982.49</v>
+        <v>297202.27</v>
       </c>
       <c r="D65" t="n">
-        <v>7649572.61</v>
+        <v>7650918.75</v>
       </c>
       <c r="E65" t="n">
-        <v>-21.2440597</v>
+        <v>-21.2320404</v>
       </c>
       <c r="F65" t="n">
-        <v>-40.9659781</v>
+        <v>-40.9540689</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Containerkade zuideinde</t>
+          <t>Wortel zuidelijke golfbreker</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>295525.07</v>
+        <v>296285.1</v>
       </c>
       <c r="D66" t="n">
-        <v>7648034.81</v>
+        <v>7647740.85</v>
       </c>
       <c r="E66" t="n">
-        <v>-21.2578946</v>
+        <v>-21.2606345</v>
       </c>
       <c r="F66" t="n">
-        <v>-40.9705687</v>
+        <v>-40.9632826</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LNG-steigerkop</t>
+          <t>Containerkade noordeinde</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>297643.11</v>
+        <v>295982.49</v>
       </c>
       <c r="D67" t="n">
-        <v>7648245.24</v>
+        <v>7649572.61</v>
       </c>
       <c r="E67" t="n">
-        <v>-21.2562317</v>
+        <v>-21.2440597</v>
       </c>
       <c r="F67" t="n">
-        <v>-40.9501407</v>
+        <v>-40.9659781</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Graankade midden</t>
+          <t>Containerkade zuideinde</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>296296.46</v>
+        <v>295525.07</v>
       </c>
       <c r="D68" t="n">
-        <v>7650045.75</v>
+        <v>7648034.81</v>
       </c>
       <c r="E68" t="n">
-        <v>-21.2398224</v>
+        <v>-21.2578946</v>
       </c>
       <c r="F68" t="n">
-        <v>-40.9628973</v>
+        <v>-40.9705687</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RoRo-kade midden</t>
+          <t>LNG-steigerkop</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>295265.72</v>
+        <v>297337.53</v>
       </c>
       <c r="D69" t="n">
-        <v>7649177.72</v>
+        <v>7648101.61</v>
       </c>
       <c r="E69" t="n">
-        <v>-21.2475449</v>
+        <v>-21.2574946</v>
       </c>
       <c r="F69" t="n">
-        <v>-40.9729295</v>
+        <v>-40.9531014</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Graankade midden</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>296296.46</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7650045.75</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-21.2398224</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-40.9628973</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RoRo-kade midden</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>295137.77</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7648747.57</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-21.2514147</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-40.9742137</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>A13</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Middelpunt draaikom binnenhaven</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>295569.79</v>
-      </c>
-      <c r="D70" t="n">
-        <v>7649774.96</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-21.242186</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-40.969929</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Middelpunt zwaaiplaats binnenhaven</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>295561.07</v>
+      </c>
+      <c r="D72" t="n">
+        <v>7649824.37</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-21.2417388</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-40.970007</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Begin bocht geul (R 3.400 m)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>301701.9</v>
+      </c>
+      <c r="D73" t="n">
+        <v>7648946.72</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-21.250345</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-40.9109605</v>
       </c>
     </row>
   </sheetData>

--- a/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
+++ b/Onderbouwing/Rekenboek_herontwerp_bijgewerkt.xlsx
@@ -10499,7 +10499,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>DO: bekkens + voorhaven, bodemmodel GEBCO 2026 + Copernicus DEM (negatief = boven MLWS, land wordt ontgraven). Celmethode met dieptezones (-18,20/-16,20/-13,70): 61.936.560 m3</t>
+          <t>DO: bekkens + voorhaven, bodemmodel GEBCO 2026 + Copernicus DEM (negatief = boven MLWS, land wordt ontgraven). Celmethode met dieptezones (-18,20/-16,20/-13,70): 61.936.561 m3</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       <c r="E24" s="32" t="n"/>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>Aanname. Celmethode: ophoging 354.822 m3, afgraving 7.346.330 m3 (terrein ligt grotendeels hoger dan +5,0 m).</t>
+          <t>Aanname. Celmethode: ophoging 355.044 m3, afgraving 7.346.682 m3 (terrein ligt grotendeels hoger dan +5,0 m).</t>
         </is>
       </c>
       <c r="G24" s="13" t="n"/>
